--- a/jogos_2025-06-20.xlsx
+++ b/jogos_2025-06-20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="142">
   <si>
     <t>Date</t>
   </si>
@@ -190,15 +190,12 @@
     <t>12:00</t>
   </si>
   <si>
-    <t>13:00</t>
+    <t>13:30</t>
   </si>
   <si>
     <t>14:00</t>
   </si>
   <si>
-    <t>15:30</t>
-  </si>
-  <si>
     <t>15:45</t>
   </si>
   <si>
@@ -226,13 +223,13 @@
     <t>Australia New South Wales NPL</t>
   </si>
   <si>
+    <t>Uzbekistan Uzbekistan Super League</t>
+  </si>
+  <si>
     <t>Belarus Vysheyshaya Liga</t>
   </si>
   <si>
-    <t>Uzbekistan Uzbekistan Super League</t>
-  </si>
-  <si>
-    <t>Italy Serie B</t>
+    <t>Chile Primera B</t>
   </si>
   <si>
     <t>Republic of Ireland First Division</t>
@@ -256,66 +253,72 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>USA NWSL</t>
+  </si>
+  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>USA NWSL</t>
-  </si>
-  <si>
     <t>2025</t>
   </si>
   <si>
-    <t>2024/2025</t>
-  </si>
-  <si>
     <t>Sydney II</t>
   </si>
   <si>
+    <t>Mash'al</t>
+  </si>
+  <si>
     <t>Smorgon</t>
   </si>
   <si>
-    <t>Navbahor</t>
+    <t>Neftchi</t>
+  </si>
+  <si>
+    <t>Unión San Felipe</t>
   </si>
   <si>
     <t>Slavia</t>
   </si>
   <si>
-    <t>Salernitana</t>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Shamrock Rovers</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Galway United</t>
   </si>
   <si>
     <t>Dundalk</t>
   </si>
   <si>
-    <t>Shamrock Rovers</t>
-  </si>
-  <si>
-    <t>Galway United</t>
-  </si>
-  <si>
     <t>Waterford</t>
   </si>
   <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
     <t>Kerry</t>
   </si>
   <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>UCD</t>
-  </si>
-  <si>
     <t>Racing Córdoba</t>
   </si>
   <si>
+    <t>Cobreloa</t>
+  </si>
+  <si>
+    <t>Recoleta</t>
+  </si>
+  <si>
     <t>Unión La Calera</t>
   </si>
   <si>
@@ -334,66 +337,75 @@
     <t>Hartford Athletic</t>
   </si>
   <si>
+    <t>Kansas City</t>
+  </si>
+  <si>
+    <t>Racing Louisville</t>
+  </si>
+  <si>
     <t>Huntsville City</t>
   </si>
   <si>
-    <t>Racing Louisville</t>
-  </si>
-  <si>
-    <t>Kansas City</t>
-  </si>
-  <si>
     <t>América Mineiro</t>
   </si>
   <si>
     <t>APIA Leichhardt Tigers</t>
   </si>
   <si>
+    <t>Nasaf</t>
+  </si>
+  <si>
     <t>Isloch</t>
   </si>
   <si>
-    <t>AGMK</t>
+    <t>Buxoro</t>
+  </si>
+  <si>
+    <t>Concepción</t>
   </si>
   <si>
     <t>BATE</t>
   </si>
   <si>
-    <t>Sampdoria</t>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>St Patrick's Athl.</t>
   </si>
   <si>
     <t>Treaty United</t>
   </si>
   <si>
-    <t>Cork City</t>
-  </si>
-  <si>
-    <t>St Patrick's Athl.</t>
-  </si>
-  <si>
     <t>Bohemians</t>
   </si>
   <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
     <t>Bray Wanderers</t>
   </si>
   <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
-    <t>Derry City</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
     <t>Deportivo Madryn</t>
   </si>
   <si>
+    <t>Curicó Unido</t>
+  </si>
+  <si>
+    <t>Deportes Temuco</t>
+  </si>
+  <si>
     <t>Universidad Católica</t>
   </si>
   <si>
@@ -412,13 +424,13 @@
     <t>Loudoun United</t>
   </si>
   <si>
+    <t>Angel City</t>
+  </si>
+  <si>
+    <t>Orlando Pride</t>
+  </si>
+  <si>
     <t>Crown Legacy</t>
-  </si>
-  <si>
-    <t>Orlando Pride</t>
-  </si>
-  <si>
-    <t>Angel City</t>
   </si>
   <si>
     <t>Criciúma</t>
@@ -791,7 +803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD27"/>
+  <dimension ref="A1:BD30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:56">
@@ -972,16 +984,16 @@
         <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" t="s">
         <v>82</v>
       </c>
-      <c r="E2" t="s">
-        <v>84</v>
-      </c>
       <c r="F2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -996,16 +1008,16 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L2">
-        <v>4.31</v>
+        <v>4.1</v>
       </c>
       <c r="M2">
-        <v>3.94</v>
+        <v>4.1</v>
       </c>
       <c r="N2">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="O2">
         <v>2.75</v>
@@ -1023,7 +1035,7 @@
         <v>3.4</v>
       </c>
       <c r="T2">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="U2">
         <v>1.57</v>
@@ -1035,22 +1047,22 @@
         <v>1.13</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="Z2">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AA2">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AB2">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AC2">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD2">
         <v>2.3</v>
@@ -1065,16 +1077,16 @@
         <v>2.25</v>
       </c>
       <c r="AH2">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="AI2">
         <v>1.2</v>
       </c>
       <c r="AJ2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AK2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AL2">
         <v>1.22</v>
@@ -1142,16 +1154,16 @@
         <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1166,16 +1178,16 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L3">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -1187,73 +1199,73 @@
         <v>0</v>
       </c>
       <c r="R3">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AC3">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AK3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AL3">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AO3">
         <v>-1</v>
@@ -1309,19 +1321,19 @@
         <v>45828</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1336,16 +1348,16 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -1357,73 +1369,73 @@
         <v>0</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AK4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AM4">
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AO4">
         <v>-1</v>
@@ -1471,7 +1483,7 @@
         <v>0</v>
       </c>
       <c r="BD4" s="3">
-        <v>45828.54166666666</v>
+        <v>45828.5</v>
       </c>
     </row>
     <row r="5" spans="1:56">
@@ -1479,19 +1491,19 @@
         <v>45828</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1506,16 +1518,16 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L5">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -1527,73 +1539,73 @@
         <v>0</v>
       </c>
       <c r="R5">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC5">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AK5" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AL5">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AO5">
         <v>-1</v>
@@ -1641,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="BD5" s="3">
-        <v>45828.58333333334</v>
+        <v>45828.5</v>
       </c>
     </row>
     <row r="6" spans="1:56">
@@ -1649,19 +1661,19 @@
         <v>45828</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1676,127 +1688,127 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L6">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="M6">
-        <v>3.07</v>
+        <v>3.23</v>
       </c>
       <c r="N6">
-        <v>3.03</v>
+        <v>2.39</v>
       </c>
       <c r="O6">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AC6">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AD6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AH6">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AK6" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AL6">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN6">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AO6">
         <v>-1</v>
       </c>
       <c r="AP6">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AQ6">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AR6">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AS6">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT6">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU6">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AV6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW6">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AX6">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY6">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AZ6">
         <v>0</v>
@@ -1805,13 +1817,13 @@
         <v>0</v>
       </c>
       <c r="BB6">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BC6">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BD6" s="3">
-        <v>45828.64583333334</v>
+        <v>45828.5625</v>
       </c>
     </row>
     <row r="7" spans="1:56">
@@ -1819,19 +1831,19 @@
         <v>45828</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1846,94 +1858,94 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L7">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="M7">
-        <v>4.44</v>
+        <v>3.8</v>
       </c>
       <c r="N7">
-        <v>7.01</v>
+        <v>4.72</v>
       </c>
       <c r="O7">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S7">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="T7">
-        <v>2.49</v>
+        <v>2.67</v>
       </c>
       <c r="U7">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="V7">
+        <v>6.3</v>
+      </c>
+      <c r="W7">
+        <v>1.06</v>
+      </c>
+      <c r="X7">
+        <v>1.01</v>
+      </c>
+      <c r="Y7">
+        <v>8.4</v>
+      </c>
+      <c r="Z7">
+        <v>1.26</v>
+      </c>
+      <c r="AA7">
+        <v>3.32</v>
+      </c>
+      <c r="AB7">
+        <v>1.85</v>
+      </c>
+      <c r="AC7">
+        <v>1.85</v>
+      </c>
+      <c r="AD7">
+        <v>3.02</v>
+      </c>
+      <c r="AE7">
+        <v>1.31</v>
+      </c>
+      <c r="AF7">
+        <v>1.9</v>
+      </c>
+      <c r="AG7">
+        <v>1.86</v>
+      </c>
+      <c r="AH7">
         <v>5.5</v>
       </c>
-      <c r="W7">
-        <v>1.11</v>
-      </c>
-      <c r="X7">
-        <v>1.04</v>
-      </c>
-      <c r="Y7">
-        <v>12</v>
-      </c>
-      <c r="Z7">
-        <v>1.22</v>
-      </c>
-      <c r="AA7">
-        <v>3.9</v>
-      </c>
-      <c r="AB7">
-        <v>1.73</v>
-      </c>
-      <c r="AC7">
-        <v>2.05</v>
-      </c>
-      <c r="AD7">
-        <v>2.8</v>
-      </c>
-      <c r="AE7">
-        <v>1.36</v>
-      </c>
-      <c r="AF7">
-        <v>1.85</v>
-      </c>
-      <c r="AG7">
-        <v>1.85</v>
-      </c>
-      <c r="AH7">
-        <v>4.75</v>
-      </c>
       <c r="AI7">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AJ7" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AK7" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AL7">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AM7">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN7">
-        <v>2.7</v>
+        <v>2.07</v>
       </c>
       <c r="AO7">
         <v>-1</v>
@@ -1975,13 +1987,13 @@
         <v>0</v>
       </c>
       <c r="BB7">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="BC7">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BD7" s="3">
-        <v>45828.65625</v>
+        <v>45828.58333333334</v>
       </c>
     </row>
     <row r="8" spans="1:56">
@@ -1989,19 +2001,19 @@
         <v>45828</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2016,127 +2028,127 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L8">
+        <v>2.75</v>
+      </c>
+      <c r="M8">
+        <v>3.17</v>
+      </c>
+      <c r="N8">
+        <v>2.27</v>
+      </c>
+      <c r="O8">
+        <v>2.1</v>
+      </c>
+      <c r="P8">
+        <v>9</v>
+      </c>
+      <c r="Q8">
+        <v>1.95</v>
+      </c>
+      <c r="R8">
+        <v>1.32</v>
+      </c>
+      <c r="S8">
+        <v>2.95</v>
+      </c>
+      <c r="T8">
+        <v>2.65</v>
+      </c>
+      <c r="U8">
+        <v>1.4</v>
+      </c>
+      <c r="V8">
+        <v>8</v>
+      </c>
+      <c r="W8">
+        <v>1.08</v>
+      </c>
+      <c r="X8">
+        <v>1.06</v>
+      </c>
+      <c r="Y8">
+        <v>9.5</v>
+      </c>
+      <c r="Z8">
+        <v>1.3</v>
+      </c>
+      <c r="AA8">
+        <v>3.3</v>
+      </c>
+      <c r="AB8">
+        <v>1.94</v>
+      </c>
+      <c r="AC8">
+        <v>1.76</v>
+      </c>
+      <c r="AD8">
+        <v>3.3</v>
+      </c>
+      <c r="AE8">
+        <v>1.29</v>
+      </c>
+      <c r="AF8">
+        <v>1.75</v>
+      </c>
+      <c r="AG8">
+        <v>2.1</v>
+      </c>
+      <c r="AH8">
+        <v>6.1</v>
+      </c>
+      <c r="AI8">
+        <v>1.08</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>141</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>141</v>
+      </c>
+      <c r="AL8">
+        <v>1.33</v>
+      </c>
+      <c r="AM8">
         <v>1.28</v>
       </c>
-      <c r="M8">
-        <v>5.2</v>
-      </c>
-      <c r="N8">
-        <v>9.4</v>
-      </c>
-      <c r="O8">
-        <v>1.18</v>
-      </c>
-      <c r="P8">
-        <v>15</v>
-      </c>
-      <c r="Q8">
-        <v>5</v>
-      </c>
-      <c r="R8">
-        <v>1.3</v>
-      </c>
-      <c r="S8">
-        <v>3.2</v>
-      </c>
-      <c r="T8">
-        <v>2.45</v>
-      </c>
-      <c r="U8">
-        <v>1.47</v>
-      </c>
-      <c r="V8">
-        <v>6.1</v>
-      </c>
-      <c r="W8">
-        <v>1.11</v>
-      </c>
-      <c r="X8">
-        <v>1.03</v>
-      </c>
-      <c r="Y8">
-        <v>9</v>
-      </c>
-      <c r="Z8">
-        <v>1.17</v>
-      </c>
-      <c r="AA8">
-        <v>4.3</v>
-      </c>
-      <c r="AB8">
-        <v>1.72</v>
-      </c>
-      <c r="AC8">
-        <v>2.07</v>
-      </c>
-      <c r="AD8">
-        <v>2.63</v>
-      </c>
-      <c r="AE8">
-        <v>1.4</v>
-      </c>
-      <c r="AF8">
-        <v>2.05</v>
-      </c>
-      <c r="AG8">
-        <v>1.67</v>
-      </c>
-      <c r="AH8">
-        <v>4.75</v>
-      </c>
-      <c r="AI8">
-        <v>1.16</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>137</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>137</v>
-      </c>
-      <c r="AL8">
-        <v>1.15</v>
-      </c>
-      <c r="AM8">
-        <v>1.15</v>
-      </c>
       <c r="AN8">
-        <v>3.3</v>
+        <v>1.44</v>
       </c>
       <c r="AO8">
         <v>-1</v>
       </c>
       <c r="AP8">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AQ8">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR8">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AS8">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AT8">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AU8">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AV8">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AW8">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX8">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AY8">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ8">
         <v>0</v>
@@ -2145,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="BB8">
-        <v>1.18</v>
+        <v>2.1</v>
       </c>
       <c r="BC8">
-        <v>5</v>
+        <v>1.95</v>
       </c>
       <c r="BD8" s="3">
         <v>45828.65625</v>
@@ -2159,19 +2171,19 @@
         <v>45828</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2186,139 +2198,139 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L9">
+        <v>1.58</v>
+      </c>
+      <c r="M9">
+        <v>3.8</v>
+      </c>
+      <c r="N9">
+        <v>4.5</v>
+      </c>
+      <c r="O9">
+        <v>1.5</v>
+      </c>
+      <c r="P9">
+        <v>13</v>
+      </c>
+      <c r="Q9">
+        <v>2.8</v>
+      </c>
+      <c r="R9">
+        <v>1.3</v>
+      </c>
+      <c r="S9">
+        <v>3.1</v>
+      </c>
+      <c r="T9">
+        <v>2.35</v>
+      </c>
+      <c r="U9">
+        <v>1.5</v>
+      </c>
+      <c r="V9">
+        <v>5</v>
+      </c>
+      <c r="W9">
+        <v>1.12</v>
+      </c>
+      <c r="X9">
+        <v>1.01</v>
+      </c>
+      <c r="Y9">
+        <v>13</v>
+      </c>
+      <c r="Z9">
+        <v>1.2</v>
+      </c>
+      <c r="AA9">
+        <v>4.2</v>
+      </c>
+      <c r="AB9">
+        <v>1.61</v>
+      </c>
+      <c r="AC9">
+        <v>2.1</v>
+      </c>
+      <c r="AD9">
         <v>2.7</v>
       </c>
-      <c r="M9">
-        <v>3.1</v>
-      </c>
-      <c r="N9">
-        <v>2.55</v>
-      </c>
-      <c r="O9">
+      <c r="AE9">
+        <v>1.44</v>
+      </c>
+      <c r="AF9">
+        <v>1.67</v>
+      </c>
+      <c r="AG9">
         <v>2.1</v>
       </c>
-      <c r="P9">
-        <v>8.6</v>
-      </c>
-      <c r="Q9">
-        <v>1.91</v>
-      </c>
-      <c r="R9">
-        <v>1.42</v>
-      </c>
-      <c r="S9">
-        <v>2.7</v>
-      </c>
-      <c r="T9">
-        <v>2.9</v>
-      </c>
-      <c r="U9">
-        <v>1.35</v>
-      </c>
-      <c r="V9">
-        <v>7.5</v>
-      </c>
-      <c r="W9">
-        <v>1.07</v>
-      </c>
-      <c r="X9">
-        <v>1.07</v>
-      </c>
-      <c r="Y9">
-        <v>6.8</v>
-      </c>
-      <c r="Z9">
-        <v>1.3</v>
-      </c>
-      <c r="AA9">
-        <v>3.2</v>
-      </c>
-      <c r="AB9">
-        <v>1.97</v>
-      </c>
-      <c r="AC9">
-        <v>1.72</v>
-      </c>
-      <c r="AD9">
-        <v>3.5</v>
-      </c>
-      <c r="AE9">
-        <v>1.25</v>
-      </c>
-      <c r="AF9">
-        <v>1.8</v>
-      </c>
-      <c r="AG9">
-        <v>1.85</v>
-      </c>
       <c r="AH9">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="AI9">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AJ9" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AK9" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AL9">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AM9">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AN9">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="AO9">
         <v>-1</v>
       </c>
       <c r="AP9">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ9">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AR9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <v>1.5</v>
+      </c>
+      <c r="BC9">
         <v>2.8</v>
-      </c>
-      <c r="AV9">
-        <v>2.12</v>
-      </c>
-      <c r="AW9">
-        <v>1.68</v>
-      </c>
-      <c r="AX9">
-        <v>1.43</v>
-      </c>
-      <c r="AY9">
-        <v>1.27</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>2.1</v>
-      </c>
-      <c r="BC9">
-        <v>1.91</v>
       </c>
       <c r="BD9" s="3">
         <v>45828.65625</v>
@@ -2329,19 +2341,19 @@
         <v>45828</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2356,127 +2368,127 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L10">
-        <v>4.33</v>
+        <v>1.38</v>
       </c>
       <c r="M10">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="N10">
-        <v>1.75</v>
+        <v>6.6</v>
       </c>
       <c r="O10">
-        <v>3</v>
+        <v>1.18</v>
       </c>
       <c r="P10">
-        <v>9.300000000000001</v>
+        <v>15</v>
       </c>
       <c r="Q10">
-        <v>1.44</v>
+        <v>5</v>
       </c>
       <c r="R10">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S10">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T10">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="U10">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="V10">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="W10">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z10">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AA10">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AB10">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AC10">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AD10">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AE10">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF10">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AG10">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AH10">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AI10">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AJ10" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AK10" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AL10">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AM10">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AN10">
-        <v>1.22</v>
+        <v>3.4</v>
       </c>
       <c r="AO10">
         <v>-1</v>
       </c>
       <c r="AP10">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ10">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AR10">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AS10">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AT10">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="AU10">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="AV10">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AW10">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AX10">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AY10">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AZ10">
         <v>0</v>
@@ -2485,10 +2497,10 @@
         <v>0</v>
       </c>
       <c r="BB10">
-        <v>3</v>
+        <v>1.18</v>
       </c>
       <c r="BC10">
-        <v>1.44</v>
+        <v>5</v>
       </c>
       <c r="BD10" s="3">
         <v>45828.65625</v>
@@ -2499,19 +2511,19 @@
         <v>45828</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
         <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2526,16 +2538,16 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L11">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="M11">
-        <v>3.97</v>
+        <v>3.3</v>
       </c>
       <c r="N11">
-        <v>4.74</v>
+        <v>4.4</v>
       </c>
       <c r="O11">
         <v>1.5</v>
@@ -2544,109 +2556,109 @@
         <v>13</v>
       </c>
       <c r="Q11">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R11">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S11">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T11">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="U11">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="V11">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W11">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>11.5</v>
+        <v>9.5</v>
       </c>
       <c r="Z11">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AA11">
-        <v>4.26</v>
+        <v>3.3</v>
       </c>
       <c r="AB11">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AC11">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AD11">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AE11">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AF11">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG11">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH11">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AI11">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AJ11" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AK11" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AL11">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AM11">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AN11">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AO11">
         <v>-1</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ11">
         <v>0</v>
@@ -2658,7 +2670,7 @@
         <v>1.5</v>
       </c>
       <c r="BC11">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="BD11" s="3">
         <v>45828.65625</v>
@@ -2669,19 +2681,19 @@
         <v>45828</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2696,16 +2708,16 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L12">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="M12">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N12">
-        <v>3.36</v>
+        <v>3.26</v>
       </c>
       <c r="O12">
         <v>1.69</v>
@@ -2723,22 +2735,22 @@
         <v>2.9</v>
       </c>
       <c r="T12">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="U12">
         <v>1.37</v>
       </c>
       <c r="V12">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>1.08</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y12">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="Z12">
         <v>1.3</v>
@@ -2747,34 +2759,34 @@
         <v>3.25</v>
       </c>
       <c r="AB12">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC12">
         <v>1.75</v>
       </c>
       <c r="AD12">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AE12">
         <v>1.25</v>
       </c>
       <c r="AF12">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG12">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH12">
-        <v>6.95</v>
+        <v>6.2</v>
       </c>
       <c r="AI12">
         <v>1.1</v>
       </c>
       <c r="AJ12" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AK12" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AL12">
         <v>1.33</v>
@@ -2839,19 +2851,19 @@
         <v>45828</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
         <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E13" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2866,127 +2878,127 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L13">
-        <v>3.16</v>
+        <v>2.29</v>
       </c>
       <c r="M13">
-        <v>3.52</v>
+        <v>2.88</v>
       </c>
       <c r="N13">
-        <v>2</v>
+        <v>2.97</v>
       </c>
       <c r="O13">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q13">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="R13">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="S13">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="T13">
-        <v>2.55</v>
+        <v>3.42</v>
       </c>
       <c r="U13">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="V13">
-        <v>5.8</v>
+        <v>8.9</v>
       </c>
       <c r="W13">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y13">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="Z13">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AA13">
-        <v>3.8</v>
+        <v>2.65</v>
       </c>
       <c r="AB13">
-        <v>1.74</v>
+        <v>2.3</v>
       </c>
       <c r="AC13">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AD13">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="AE13">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="AF13">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AG13">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AH13">
-        <v>5.24</v>
+        <v>9.1</v>
       </c>
       <c r="AI13">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AJ13" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AK13" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AL13">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN13">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AO13">
         <v>-1</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ13">
         <v>0</v>
@@ -2995,10 +3007,10 @@
         <v>0</v>
       </c>
       <c r="BB13">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="BC13">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="BD13" s="3">
         <v>45828.65625</v>
@@ -3009,19 +3021,19 @@
         <v>45828</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E14" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -3036,127 +3048,127 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L14">
-        <v>1.67</v>
+        <v>2.57</v>
       </c>
       <c r="M14">
-        <v>3.82</v>
+        <v>3.07</v>
       </c>
       <c r="N14">
-        <v>4.49</v>
+        <v>2.47</v>
       </c>
       <c r="O14">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="P14">
-        <v>13</v>
+        <v>8.6</v>
       </c>
       <c r="Q14">
-        <v>2.88</v>
+        <v>1.91</v>
       </c>
       <c r="R14">
+        <v>1.42</v>
+      </c>
+      <c r="S14">
+        <v>2.62</v>
+      </c>
+      <c r="T14">
+        <v>2.9</v>
+      </c>
+      <c r="U14">
+        <v>1.36</v>
+      </c>
+      <c r="V14">
+        <v>7.9</v>
+      </c>
+      <c r="W14">
+        <v>1.07</v>
+      </c>
+      <c r="X14">
+        <v>1.06</v>
+      </c>
+      <c r="Y14">
+        <v>8</v>
+      </c>
+      <c r="Z14">
+        <v>1.3</v>
+      </c>
+      <c r="AA14">
+        <v>3.1</v>
+      </c>
+      <c r="AB14">
+        <v>1.87</v>
+      </c>
+      <c r="AC14">
+        <v>1.83</v>
+      </c>
+      <c r="AD14">
+        <v>3.5</v>
+      </c>
+      <c r="AE14">
+        <v>1.25</v>
+      </c>
+      <c r="AF14">
+        <v>1.8</v>
+      </c>
+      <c r="AG14">
+        <v>1.91</v>
+      </c>
+      <c r="AH14">
+        <v>7</v>
+      </c>
+      <c r="AI14">
+        <v>1.08</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>141</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>141</v>
+      </c>
+      <c r="AL14">
         <v>1.33</v>
       </c>
-      <c r="S14">
-        <v>3</v>
-      </c>
-      <c r="T14">
-        <v>2.65</v>
-      </c>
-      <c r="U14">
-        <v>1.42</v>
-      </c>
-      <c r="V14">
-        <v>6.5</v>
-      </c>
-      <c r="W14">
-        <v>1.1</v>
-      </c>
-      <c r="X14">
-        <v>1.01</v>
-      </c>
-      <c r="Y14">
-        <v>10</v>
-      </c>
-      <c r="Z14">
-        <v>1.25</v>
-      </c>
-      <c r="AA14">
-        <v>3.6</v>
-      </c>
-      <c r="AB14">
-        <v>1.8</v>
-      </c>
-      <c r="AC14">
-        <v>1.91</v>
-      </c>
-      <c r="AD14">
-        <v>3.2</v>
-      </c>
-      <c r="AE14">
-        <v>1.33</v>
-      </c>
-      <c r="AF14">
-        <v>1.73</v>
-      </c>
-      <c r="AG14">
-        <v>1.95</v>
-      </c>
-      <c r="AH14">
-        <v>5.8</v>
-      </c>
-      <c r="AI14">
-        <v>1.13</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>137</v>
-      </c>
-      <c r="AK14" t="s">
-        <v>137</v>
-      </c>
-      <c r="AL14">
-        <v>1.29</v>
-      </c>
       <c r="AM14">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AN14">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AO14">
         <v>-1</v>
       </c>
       <c r="AP14">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AQ14">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AR14">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AS14">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="AT14">
+        <v>3.5</v>
+      </c>
+      <c r="AU14">
         <v>3.05</v>
       </c>
-      <c r="AU14">
-        <v>3.1</v>
-      </c>
       <c r="AV14">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AW14">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AX14">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AY14">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AZ14">
         <v>0</v>
@@ -3165,10 +3177,10 @@
         <v>0</v>
       </c>
       <c r="BB14">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="BC14">
-        <v>2.88</v>
+        <v>1.91</v>
       </c>
       <c r="BD14" s="3">
         <v>45828.65625</v>
@@ -3179,19 +3191,19 @@
         <v>45828</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E15" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3206,127 +3218,127 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L15">
+        <v>1.37</v>
+      </c>
+      <c r="M15">
+        <v>4.2</v>
+      </c>
+      <c r="N15">
+        <v>6.4</v>
+      </c>
+      <c r="O15">
+        <v>1.34</v>
+      </c>
+      <c r="P15">
+        <v>13</v>
+      </c>
+      <c r="Q15">
+        <v>3.4</v>
+      </c>
+      <c r="R15">
+        <v>1.3</v>
+      </c>
+      <c r="S15">
+        <v>3.1</v>
+      </c>
+      <c r="T15">
         <v>2.54</v>
       </c>
-      <c r="M15">
-        <v>3</v>
-      </c>
-      <c r="N15">
-        <v>2.85</v>
-      </c>
-      <c r="O15">
-        <v>1.91</v>
-      </c>
-      <c r="P15">
-        <v>6.4</v>
-      </c>
-      <c r="Q15">
-        <v>2.25</v>
-      </c>
-      <c r="R15">
-        <v>1.52</v>
-      </c>
-      <c r="S15">
-        <v>2.35</v>
-      </c>
-      <c r="T15">
-        <v>3.4</v>
-      </c>
       <c r="U15">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="V15">
-        <v>8.9</v>
+        <v>5</v>
       </c>
       <c r="W15">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X15">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="Z15">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="AA15">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="AB15">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="AC15">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AD15">
-        <v>4.75</v>
+        <v>2.23</v>
       </c>
       <c r="AE15">
-        <v>1.17</v>
+        <v>1.54</v>
       </c>
       <c r="AF15">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG15">
         <v>1.8</v>
       </c>
       <c r="AH15">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="AI15">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AJ15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AK15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AL15">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AM15">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AN15">
-        <v>1.44</v>
+        <v>2.8</v>
       </c>
       <c r="AO15">
         <v>-1</v>
       </c>
       <c r="AP15">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ15">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AR15">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AS15">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AT15">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AU15">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV15">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AW15">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AX15">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AY15">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AZ15">
         <v>0</v>
@@ -3335,10 +3347,10 @@
         <v>0</v>
       </c>
       <c r="BB15">
-        <v>1.91</v>
+        <v>1.34</v>
       </c>
       <c r="BC15">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="BD15" s="3">
         <v>45828.65625</v>
@@ -3349,19 +3361,19 @@
         <v>45828</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s">
         <v>73</v>
       </c>
       <c r="D16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E16" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3376,127 +3388,127 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L16">
-        <v>2.61</v>
+        <v>3.82</v>
       </c>
       <c r="M16">
-        <v>3.26</v>
+        <v>3.47</v>
       </c>
       <c r="N16">
-        <v>2.55</v>
+        <v>1.76</v>
       </c>
       <c r="O16">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="P16">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q16">
+        <v>1.44</v>
+      </c>
+      <c r="R16">
+        <v>1.33</v>
+      </c>
+      <c r="S16">
+        <v>3.11</v>
+      </c>
+      <c r="T16">
+        <v>2.62</v>
+      </c>
+      <c r="U16">
+        <v>1.44</v>
+      </c>
+      <c r="V16">
+        <v>6.5</v>
+      </c>
+      <c r="W16">
+        <v>1.09</v>
+      </c>
+      <c r="X16">
+        <v>1.02</v>
+      </c>
+      <c r="Y16">
+        <v>10</v>
+      </c>
+      <c r="Z16">
+        <v>1.24</v>
+      </c>
+      <c r="AA16">
+        <v>3.6</v>
+      </c>
+      <c r="AB16">
+        <v>1.83</v>
+      </c>
+      <c r="AC16">
+        <v>1.87</v>
+      </c>
+      <c r="AD16">
+        <v>2.97</v>
+      </c>
+      <c r="AE16">
+        <v>1.36</v>
+      </c>
+      <c r="AF16">
+        <v>1.76</v>
+      </c>
+      <c r="AG16">
         <v>1.95</v>
       </c>
-      <c r="R16">
-        <v>1.35</v>
-      </c>
-      <c r="S16">
-        <v>2.8</v>
-      </c>
-      <c r="T16">
-        <v>2.9</v>
-      </c>
-      <c r="U16">
-        <v>1.33</v>
-      </c>
-      <c r="V16">
-        <v>6</v>
-      </c>
-      <c r="W16">
-        <v>1.08</v>
-      </c>
-      <c r="X16">
-        <v>1.06</v>
-      </c>
-      <c r="Y16">
-        <v>9</v>
-      </c>
-      <c r="Z16">
-        <v>1.33</v>
-      </c>
-      <c r="AA16">
-        <v>3.2</v>
-      </c>
-      <c r="AB16">
-        <v>2.02</v>
-      </c>
-      <c r="AC16">
-        <v>1.75</v>
-      </c>
-      <c r="AD16">
-        <v>3.45</v>
-      </c>
-      <c r="AE16">
+      <c r="AH16">
+        <v>5.92</v>
+      </c>
+      <c r="AI16">
+        <v>1.12</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>141</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>141</v>
+      </c>
+      <c r="AL16">
         <v>1.25</v>
       </c>
-      <c r="AF16">
-        <v>1.75</v>
-      </c>
-      <c r="AG16">
-        <v>2.05</v>
-      </c>
-      <c r="AH16">
-        <v>6.43</v>
-      </c>
-      <c r="AI16">
-        <v>1.05</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>137</v>
-      </c>
-      <c r="AK16" t="s">
-        <v>137</v>
-      </c>
-      <c r="AL16">
-        <v>1.33</v>
-      </c>
       <c r="AM16">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AN16">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AO16">
         <v>-1</v>
       </c>
       <c r="AP16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AU16">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AV16">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AW16">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AY16">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ16">
         <v>0</v>
@@ -3505,10 +3517,10 @@
         <v>0</v>
       </c>
       <c r="BB16">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="BC16">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="BD16" s="3">
         <v>45828.65625</v>
@@ -3519,19 +3531,19 @@
         <v>45828</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E17" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3546,94 +3558,94 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L17">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="M17">
-        <v>2.45</v>
+        <v>3.41</v>
       </c>
       <c r="N17">
-        <v>3.1</v>
+        <v>2.02</v>
       </c>
       <c r="O17">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="P17">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>2.63</v>
+        <v>1.62</v>
       </c>
       <c r="R17">
+        <v>1.31</v>
+      </c>
+      <c r="S17">
+        <v>3.14</v>
+      </c>
+      <c r="T17">
+        <v>2.55</v>
+      </c>
+      <c r="U17">
+        <v>1.42</v>
+      </c>
+      <c r="V17">
+        <v>5.5</v>
+      </c>
+      <c r="W17">
+        <v>1.09</v>
+      </c>
+      <c r="X17">
+        <v>1.05</v>
+      </c>
+      <c r="Y17">
+        <v>11</v>
+      </c>
+      <c r="Z17">
+        <v>1.25</v>
+      </c>
+      <c r="AA17">
+        <v>3.8</v>
+      </c>
+      <c r="AB17">
+        <v>1.7</v>
+      </c>
+      <c r="AC17">
+        <v>1.95</v>
+      </c>
+      <c r="AD17">
+        <v>3</v>
+      </c>
+      <c r="AE17">
+        <v>1.36</v>
+      </c>
+      <c r="AF17">
         <v>1.67</v>
       </c>
-      <c r="S17">
-        <v>2</v>
-      </c>
-      <c r="T17">
-        <v>4.33</v>
-      </c>
-      <c r="U17">
-        <v>1.17</v>
-      </c>
-      <c r="V17">
-        <v>11</v>
-      </c>
-      <c r="W17">
-        <v>1.01</v>
-      </c>
-      <c r="X17">
-        <v>1.17</v>
-      </c>
-      <c r="Y17">
-        <v>4.9</v>
-      </c>
-      <c r="Z17">
-        <v>1.69</v>
-      </c>
-      <c r="AA17">
-        <v>2.1</v>
-      </c>
-      <c r="AB17">
-        <v>3.4</v>
-      </c>
-      <c r="AC17">
-        <v>1.32</v>
-      </c>
-      <c r="AD17">
-        <v>5.88</v>
-      </c>
-      <c r="AE17">
-        <v>1.11</v>
-      </c>
-      <c r="AF17">
-        <v>2.3</v>
-      </c>
       <c r="AG17">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
       <c r="AH17">
-        <v>8.699999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="AI17">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AJ17" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AK17" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AL17">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AM17">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AN17">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AO17">
         <v>-1</v>
@@ -3675,13 +3687,13 @@
         <v>0</v>
       </c>
       <c r="BB17">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="BC17">
-        <v>2.63</v>
+        <v>1.62</v>
       </c>
       <c r="BD17" s="3">
-        <v>45828.66666666666</v>
+        <v>45828.65625</v>
       </c>
     </row>
     <row r="18" spans="1:56">
@@ -3689,19 +3701,19 @@
         <v>45828</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -3716,127 +3728,127 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L18">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="M18">
-        <v>3.2</v>
+        <v>2.79</v>
       </c>
       <c r="N18">
-        <v>2.65</v>
+        <v>3.67</v>
       </c>
       <c r="O18">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="P18">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="Q18">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="R18">
+        <v>1.67</v>
+      </c>
+      <c r="S18">
+        <v>2</v>
+      </c>
+      <c r="T18">
+        <v>4.33</v>
+      </c>
+      <c r="U18">
+        <v>1.17</v>
+      </c>
+      <c r="V18">
+        <v>11</v>
+      </c>
+      <c r="W18">
+        <v>1.02</v>
+      </c>
+      <c r="X18">
+        <v>1.13</v>
+      </c>
+      <c r="Y18">
+        <v>4.75</v>
+      </c>
+      <c r="Z18">
+        <v>1.65</v>
+      </c>
+      <c r="AA18">
+        <v>2.1</v>
+      </c>
+      <c r="AB18">
+        <v>2.3</v>
+      </c>
+      <c r="AC18">
+        <v>1.5</v>
+      </c>
+      <c r="AD18">
+        <v>5.88</v>
+      </c>
+      <c r="AE18">
+        <v>1.11</v>
+      </c>
+      <c r="AF18">
+        <v>2.3</v>
+      </c>
+      <c r="AG18">
+        <v>1.55</v>
+      </c>
+      <c r="AH18">
+        <v>14</v>
+      </c>
+      <c r="AI18">
+        <v>1</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>141</v>
+      </c>
+      <c r="AK18" t="s">
+        <v>141</v>
+      </c>
+      <c r="AL18">
+        <v>1.53</v>
+      </c>
+      <c r="AM18">
         <v>1.48</v>
       </c>
-      <c r="S18">
-        <v>2.48</v>
-      </c>
-      <c r="T18">
-        <v>3.3</v>
-      </c>
-      <c r="U18">
-        <v>1.29</v>
-      </c>
-      <c r="V18">
-        <v>8</v>
-      </c>
-      <c r="W18">
-        <v>1.04</v>
-      </c>
-      <c r="X18">
-        <v>1.05</v>
-      </c>
-      <c r="Y18">
-        <v>8</v>
-      </c>
-      <c r="Z18">
-        <v>1.36</v>
-      </c>
-      <c r="AA18">
-        <v>2.88</v>
-      </c>
-      <c r="AB18">
-        <v>2.28</v>
-      </c>
-      <c r="AC18">
-        <v>1.58</v>
-      </c>
-      <c r="AD18">
-        <v>4.5</v>
-      </c>
-      <c r="AE18">
-        <v>1.17</v>
-      </c>
-      <c r="AF18">
-        <v>1.91</v>
-      </c>
-      <c r="AG18">
-        <v>1.77</v>
-      </c>
-      <c r="AH18">
-        <v>9</v>
-      </c>
-      <c r="AI18">
-        <v>1.03</v>
-      </c>
-      <c r="AJ18" t="s">
-        <v>137</v>
-      </c>
-      <c r="AK18" t="s">
-        <v>137</v>
-      </c>
-      <c r="AL18">
-        <v>1.46</v>
-      </c>
-      <c r="AM18">
-        <v>1.33</v>
-      </c>
       <c r="AN18">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AO18">
         <v>-1</v>
       </c>
       <c r="AP18">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ18">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AR18">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AS18">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AT18">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AU18">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AV18">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AW18">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AX18">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY18">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ18">
         <v>0</v>
@@ -3845,13 +3857,13 @@
         <v>0</v>
       </c>
       <c r="BB18">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="BC18">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="BD18" s="3">
-        <v>45828.77083333334</v>
+        <v>45828.66666666666</v>
       </c>
     </row>
     <row r="19" spans="1:56">
@@ -3859,19 +3871,19 @@
         <v>45828</v>
       </c>
       <c r="B19" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E19" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -3886,16 +3898,16 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -3937,10 +3949,10 @@
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD19">
         <v>0</v>
@@ -3961,10 +3973,10 @@
         <v>0</v>
       </c>
       <c r="AJ19" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AK19" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4021,7 +4033,7 @@
         <v>0</v>
       </c>
       <c r="BD19" s="3">
-        <v>45828.79166666666</v>
+        <v>45828.66666666666</v>
       </c>
     </row>
     <row r="20" spans="1:56">
@@ -4029,19 +4041,19 @@
         <v>45828</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F20" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -4056,127 +4068,127 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L20">
-        <v>2.7</v>
+        <v>2.11</v>
       </c>
       <c r="M20">
-        <v>3.01</v>
+        <v>3.17</v>
       </c>
       <c r="N20">
-        <v>2.87</v>
+        <v>3.03</v>
       </c>
       <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
         <v>2.2</v>
       </c>
-      <c r="P20">
-        <v>6.25</v>
-      </c>
-      <c r="Q20">
-        <v>1.95</v>
-      </c>
-      <c r="R20">
-        <v>1.57</v>
-      </c>
-      <c r="S20">
-        <v>2.36</v>
-      </c>
-      <c r="T20">
-        <v>3.6</v>
-      </c>
-      <c r="U20">
-        <v>1.24</v>
-      </c>
-      <c r="V20">
-        <v>10</v>
-      </c>
-      <c r="W20">
-        <v>1.02</v>
-      </c>
-      <c r="X20">
-        <v>1.11</v>
-      </c>
-      <c r="Y20">
-        <v>6.5</v>
-      </c>
-      <c r="Z20">
-        <v>1.5</v>
-      </c>
-      <c r="AA20">
-        <v>2.45</v>
-      </c>
-      <c r="AB20">
-        <v>2.45</v>
-      </c>
       <c r="AC20">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AD20">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AE20">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF20">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG20">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH20">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AI20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AK20" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AL20">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AM20">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN20">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO20">
         <v>-1</v>
       </c>
       <c r="AP20">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ20">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AR20">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AS20">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AT20">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AU20">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AV20">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AW20">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AX20">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AY20">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ20">
         <v>0</v>
@@ -4185,13 +4197,13 @@
         <v>0</v>
       </c>
       <c r="BB20">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BC20">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD20" s="3">
-        <v>45828.79166666666</v>
+        <v>45828.66666666666</v>
       </c>
     </row>
     <row r="21" spans="1:56">
@@ -4199,19 +4211,19 @@
         <v>45828</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E21" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -4226,127 +4238,127 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L21">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="M21">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="N21">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="O21">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="P21">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q21">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="R21">
+        <v>1.48</v>
+      </c>
+      <c r="S21">
+        <v>2.48</v>
+      </c>
+      <c r="T21">
+        <v>3.3</v>
+      </c>
+      <c r="U21">
+        <v>1.29</v>
+      </c>
+      <c r="V21">
+        <v>8</v>
+      </c>
+      <c r="W21">
+        <v>1.04</v>
+      </c>
+      <c r="X21">
+        <v>1.05</v>
+      </c>
+      <c r="Y21">
+        <v>8</v>
+      </c>
+      <c r="Z21">
         <v>1.36</v>
       </c>
-      <c r="S21">
-        <v>2.85</v>
-      </c>
-      <c r="T21">
-        <v>2.5</v>
-      </c>
-      <c r="U21">
-        <v>1.45</v>
-      </c>
-      <c r="V21">
-        <v>6.65</v>
-      </c>
-      <c r="W21">
-        <v>1.09</v>
-      </c>
-      <c r="X21">
-        <v>1</v>
-      </c>
-      <c r="Y21">
-        <v>10.4</v>
-      </c>
-      <c r="Z21">
-        <v>1.25</v>
-      </c>
       <c r="AA21">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="AB21">
-        <v>1.78</v>
+        <v>2.28</v>
       </c>
       <c r="AC21">
+        <v>1.58</v>
+      </c>
+      <c r="AD21">
+        <v>4.5</v>
+      </c>
+      <c r="AE21">
+        <v>1.17</v>
+      </c>
+      <c r="AF21">
         <v>1.91</v>
       </c>
-      <c r="AD21">
-        <v>2.8</v>
-      </c>
-      <c r="AE21">
+      <c r="AG21">
+        <v>1.77</v>
+      </c>
+      <c r="AH21">
+        <v>9</v>
+      </c>
+      <c r="AI21">
+        <v>1.03</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>141</v>
+      </c>
+      <c r="AK21" t="s">
+        <v>141</v>
+      </c>
+      <c r="AL21">
+        <v>1.46</v>
+      </c>
+      <c r="AM21">
         <v>1.33</v>
       </c>
-      <c r="AF21">
-        <v>1.6</v>
-      </c>
-      <c r="AG21">
-        <v>2.15</v>
-      </c>
-      <c r="AH21">
-        <v>5.2</v>
-      </c>
-      <c r="AI21">
-        <v>1.08</v>
-      </c>
-      <c r="AJ21" t="s">
-        <v>137</v>
-      </c>
-      <c r="AK21" t="s">
-        <v>137</v>
-      </c>
-      <c r="AL21">
-        <v>1.35</v>
-      </c>
-      <c r="AM21">
-        <v>1.31</v>
-      </c>
       <c r="AN21">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AO21">
         <v>-1</v>
       </c>
       <c r="AP21">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AU21">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AV21">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AW21">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX21">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY21">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ21">
         <v>0</v>
@@ -4355,13 +4367,13 @@
         <v>0</v>
       </c>
       <c r="BB21">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="BC21">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="BD21" s="3">
-        <v>45828.83333333334</v>
+        <v>45828.77083333334</v>
       </c>
     </row>
     <row r="22" spans="1:56">
@@ -4369,19 +4381,19 @@
         <v>45828</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E22" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -4396,94 +4408,94 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L22">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD22">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH22">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI22">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AK22" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AL22">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AM22">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN22">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AO22">
         <v>-1</v>
@@ -4525,13 +4537,13 @@
         <v>0</v>
       </c>
       <c r="BB22">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BC22">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BD22" s="3">
-        <v>45828.85416666666</v>
+        <v>45828.79166666666</v>
       </c>
     </row>
     <row r="23" spans="1:56">
@@ -4539,19 +4551,19 @@
         <v>45828</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E23" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F23" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -4566,127 +4578,127 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L23">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="M23">
-        <v>3.5</v>
+        <v>2.94</v>
       </c>
       <c r="N23">
-        <v>1.9</v>
+        <v>2.17</v>
       </c>
       <c r="O23">
+        <v>2.2</v>
+      </c>
+      <c r="P23">
+        <v>6.25</v>
+      </c>
+      <c r="Q23">
+        <v>1.95</v>
+      </c>
+      <c r="R23">
+        <v>1.55</v>
+      </c>
+      <c r="S23">
+        <v>2.2</v>
+      </c>
+      <c r="T23">
+        <v>3.58</v>
+      </c>
+      <c r="U23">
+        <v>1.25</v>
+      </c>
+      <c r="V23">
+        <v>10</v>
+      </c>
+      <c r="W23">
+        <v>1.04</v>
+      </c>
+      <c r="X23">
+        <v>1.09</v>
+      </c>
+      <c r="Y23">
+        <v>6</v>
+      </c>
+      <c r="Z23">
+        <v>1.55</v>
+      </c>
+      <c r="AA23">
+        <v>2.38</v>
+      </c>
+      <c r="AB23">
         <v>2.3</v>
       </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>1.67</v>
-      </c>
-      <c r="R23">
-        <v>1.35</v>
-      </c>
-      <c r="S23">
-        <v>2.85</v>
-      </c>
-      <c r="T23">
-        <v>2.35</v>
-      </c>
-      <c r="U23">
+      <c r="AC23">
         <v>1.5</v>
       </c>
-      <c r="V23">
-        <v>5</v>
-      </c>
-      <c r="W23">
-        <v>1.12</v>
-      </c>
-      <c r="X23">
+      <c r="AD23">
+        <v>5.44</v>
+      </c>
+      <c r="AE23">
+        <v>1.15</v>
+      </c>
+      <c r="AF23">
+        <v>2.05</v>
+      </c>
+      <c r="AG23">
+        <v>1.7</v>
+      </c>
+      <c r="AH23">
+        <v>11</v>
+      </c>
+      <c r="AI23">
         <v>1.02</v>
       </c>
-      <c r="Y23">
-        <v>10</v>
-      </c>
-      <c r="Z23">
-        <v>1.22</v>
-      </c>
-      <c r="AA23">
-        <v>3.8</v>
-      </c>
-      <c r="AB23">
-        <v>1.7</v>
-      </c>
-      <c r="AC23">
-        <v>2</v>
-      </c>
-      <c r="AD23">
-        <v>2.7</v>
-      </c>
-      <c r="AE23">
-        <v>1.42</v>
-      </c>
-      <c r="AF23">
-        <v>1.57</v>
-      </c>
-      <c r="AG23">
-        <v>2.2</v>
-      </c>
-      <c r="AH23">
-        <v>5.05</v>
-      </c>
-      <c r="AI23">
-        <v>1.13</v>
-      </c>
       <c r="AJ23" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AK23" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AL23">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN23">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AO23">
         <v>-1</v>
       </c>
       <c r="AP23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AU23">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AV23">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AW23">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX23">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY23">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ23">
         <v>0</v>
@@ -4695,13 +4707,13 @@
         <v>0</v>
       </c>
       <c r="BB23">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="BC23">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="BD23" s="3">
-        <v>45828.85416666666</v>
+        <v>45828.79166666666</v>
       </c>
     </row>
     <row r="24" spans="1:56">
@@ -4709,19 +4721,19 @@
         <v>45828</v>
       </c>
       <c r="B24" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E24" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F24" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -4736,94 +4748,94 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AK24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO24">
         <v>-1</v>
@@ -4865,13 +4877,13 @@
         <v>0</v>
       </c>
       <c r="BB24">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BC24">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD24" s="3">
-        <v>45828.875</v>
+        <v>45828.83333333334</v>
       </c>
     </row>
     <row r="25" spans="1:56">
@@ -4879,19 +4891,19 @@
         <v>45828</v>
       </c>
       <c r="B25" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" t="s">
         <v>81</v>
       </c>
-      <c r="D25" t="s">
-        <v>82</v>
-      </c>
       <c r="E25" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -4906,94 +4918,94 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L25">
-        <v>4.63</v>
+        <v>3</v>
       </c>
       <c r="M25">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="N25">
+        <v>2.07</v>
+      </c>
+      <c r="O25">
+        <v>2.3</v>
+      </c>
+      <c r="P25">
+        <v>13.5</v>
+      </c>
+      <c r="Q25">
+        <v>1.67</v>
+      </c>
+      <c r="R25">
+        <v>1.35</v>
+      </c>
+      <c r="S25">
+        <v>2.85</v>
+      </c>
+      <c r="T25">
+        <v>2.55</v>
+      </c>
+      <c r="U25">
+        <v>1.45</v>
+      </c>
+      <c r="V25">
+        <v>6.15</v>
+      </c>
+      <c r="W25">
+        <v>1.09</v>
+      </c>
+      <c r="X25">
+        <v>1.02</v>
+      </c>
+      <c r="Y25">
+        <v>10</v>
+      </c>
+      <c r="Z25">
+        <v>1.25</v>
+      </c>
+      <c r="AA25">
+        <v>3.8</v>
+      </c>
+      <c r="AB25">
         <v>1.75</v>
       </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>0</v>
-      </c>
-      <c r="Q25">
-        <v>0</v>
-      </c>
-      <c r="R25">
-        <v>1.45</v>
-      </c>
-      <c r="S25">
-        <v>2.4</v>
-      </c>
-      <c r="T25">
-        <v>3.28</v>
-      </c>
-      <c r="U25">
-        <v>1.3</v>
-      </c>
-      <c r="V25">
-        <v>8.5</v>
-      </c>
-      <c r="W25">
-        <v>1.04</v>
-      </c>
-      <c r="X25">
-        <v>1.06</v>
-      </c>
-      <c r="Y25">
-        <v>6.26</v>
-      </c>
-      <c r="Z25">
+      <c r="AC25">
+        <v>1.97</v>
+      </c>
+      <c r="AD25">
+        <v>2.8</v>
+      </c>
+      <c r="AE25">
         <v>1.37</v>
       </c>
-      <c r="AA25">
-        <v>2.66</v>
-      </c>
-      <c r="AB25">
-        <v>2.25</v>
-      </c>
-      <c r="AC25">
-        <v>1.56</v>
-      </c>
-      <c r="AD25">
-        <v>4.3</v>
-      </c>
-      <c r="AE25">
-        <v>1.15</v>
-      </c>
       <c r="AF25">
+        <v>1.62</v>
+      </c>
+      <c r="AG25">
         <v>2.1</v>
       </c>
-      <c r="AG25">
-        <v>1.65</v>
-      </c>
       <c r="AH25">
-        <v>8.5</v>
+        <v>4.8</v>
       </c>
       <c r="AI25">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AJ25" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AK25" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AL25">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AM25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN25">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AO25">
         <v>-1</v>
@@ -5035,13 +5047,13 @@
         <v>0</v>
       </c>
       <c r="BB25">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BC25">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BD25" s="3">
-        <v>45828.875</v>
+        <v>45828.85416666666</v>
       </c>
     </row>
     <row r="26" spans="1:56">
@@ -5049,19 +5061,19 @@
         <v>45828</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" t="s">
         <v>81</v>
       </c>
-      <c r="D26" t="s">
-        <v>82</v>
-      </c>
       <c r="E26" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F26" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5076,94 +5088,94 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L26">
-        <v>1.49</v>
+        <v>4.4</v>
       </c>
       <c r="M26">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="N26">
-        <v>5.2</v>
+        <v>1.61</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P26">
         <v>0</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R26">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S26">
-        <v>2.72</v>
+        <v>2.85</v>
       </c>
       <c r="T26">
+        <v>2.5</v>
+      </c>
+      <c r="U26">
+        <v>1.45</v>
+      </c>
+      <c r="V26">
+        <v>5.5</v>
+      </c>
+      <c r="W26">
+        <v>1.1</v>
+      </c>
+      <c r="X26">
+        <v>1.02</v>
+      </c>
+      <c r="Y26">
+        <v>10</v>
+      </c>
+      <c r="Z26">
+        <v>1.22</v>
+      </c>
+      <c r="AA26">
+        <v>3.8</v>
+      </c>
+      <c r="AB26">
+        <v>1.69</v>
+      </c>
+      <c r="AC26">
+        <v>2.05</v>
+      </c>
+      <c r="AD26">
         <v>2.9</v>
       </c>
-      <c r="U26">
-        <v>1.33</v>
-      </c>
-      <c r="V26">
-        <v>7.3</v>
-      </c>
-      <c r="W26">
-        <v>1.07</v>
-      </c>
-      <c r="X26">
-        <v>1.03</v>
-      </c>
-      <c r="Y26">
-        <v>8.5</v>
-      </c>
-      <c r="Z26">
-        <v>1.29</v>
-      </c>
-      <c r="AA26">
-        <v>3.04</v>
-      </c>
-      <c r="AB26">
-        <v>1.99</v>
-      </c>
-      <c r="AC26">
-        <v>1.72</v>
-      </c>
-      <c r="AD26">
-        <v>3.4</v>
-      </c>
       <c r="AE26">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="AF26">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AG26">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AH26">
         <v>5.2</v>
       </c>
       <c r="AI26">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AJ26" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AK26" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AL26">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AM26">
         <v>0</v>
       </c>
       <c r="AN26">
-        <v>2.05</v>
+        <v>1.22</v>
       </c>
       <c r="AO26">
         <v>-1</v>
@@ -5205,13 +5217,13 @@
         <v>0</v>
       </c>
       <c r="BB26">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BC26">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BD26" s="3">
-        <v>45828.875</v>
+        <v>45828.85416666666</v>
       </c>
     </row>
     <row r="27" spans="1:56">
@@ -5219,19 +5231,19 @@
         <v>45828</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E27" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F27" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -5246,141 +5258,651 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L27">
-        <v>1.82</v>
+        <v>1.49</v>
       </c>
       <c r="M27">
-        <v>3.34</v>
+        <v>3.95</v>
       </c>
       <c r="N27">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="O27">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="S27">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="T27">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U27">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V27">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X27">
+        <v>1.03</v>
+      </c>
+      <c r="Y27">
+        <v>7.65</v>
+      </c>
+      <c r="Z27">
+        <v>1.33</v>
+      </c>
+      <c r="AA27">
+        <v>3.04</v>
+      </c>
+      <c r="AB27">
+        <v>1.75</v>
+      </c>
+      <c r="AC27">
+        <v>1.95</v>
+      </c>
+      <c r="AD27">
+        <v>3.4</v>
+      </c>
+      <c r="AE27">
+        <v>1.22</v>
+      </c>
+      <c r="AF27">
+        <v>1.95</v>
+      </c>
+      <c r="AG27">
+        <v>1.75</v>
+      </c>
+      <c r="AH27">
+        <v>6.1</v>
+      </c>
+      <c r="AI27">
         <v>1.08</v>
       </c>
-      <c r="Y27">
-        <v>6.5</v>
-      </c>
-      <c r="Z27">
-        <v>1.38</v>
-      </c>
-      <c r="AA27">
-        <v>2.9</v>
-      </c>
-      <c r="AB27">
-        <v>2.2</v>
-      </c>
-      <c r="AC27">
-        <v>1.6</v>
-      </c>
-      <c r="AD27">
-        <v>4.22</v>
-      </c>
-      <c r="AE27">
-        <v>1.2</v>
-      </c>
-      <c r="AF27">
+      <c r="AJ27" t="s">
+        <v>141</v>
+      </c>
+      <c r="AK27" t="s">
+        <v>141</v>
+      </c>
+      <c r="AL27">
+        <v>1.18</v>
+      </c>
+      <c r="AM27">
+        <v>0</v>
+      </c>
+      <c r="AN27">
         <v>2.05</v>
-      </c>
-      <c r="AG27">
-        <v>1.7</v>
-      </c>
-      <c r="AH27">
-        <v>8.5</v>
-      </c>
-      <c r="AI27">
-        <v>1.06</v>
-      </c>
-      <c r="AJ27" t="s">
-        <v>137</v>
-      </c>
-      <c r="AK27" t="s">
-        <v>137</v>
-      </c>
-      <c r="AL27">
-        <v>1.3</v>
-      </c>
-      <c r="AM27">
-        <v>1.31</v>
-      </c>
-      <c r="AN27">
-        <v>1.77</v>
       </c>
       <c r="AO27">
         <v>-1</v>
       </c>
       <c r="AP27">
+        <v>0</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27">
+        <v>0</v>
+      </c>
+      <c r="AV27">
+        <v>0</v>
+      </c>
+      <c r="AW27">
+        <v>0</v>
+      </c>
+      <c r="AX27">
+        <v>0</v>
+      </c>
+      <c r="AY27">
+        <v>0</v>
+      </c>
+      <c r="AZ27">
+        <v>0</v>
+      </c>
+      <c r="BA27">
+        <v>0</v>
+      </c>
+      <c r="BB27">
+        <v>0</v>
+      </c>
+      <c r="BC27">
+        <v>0</v>
+      </c>
+      <c r="BD27" s="3">
+        <v>45828.875</v>
+      </c>
+    </row>
+    <row r="28" spans="1:56">
+      <c r="A28" s="2">
+        <v>45828</v>
+      </c>
+      <c r="B28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" t="s">
+        <v>81</v>
+      </c>
+      <c r="E28" t="s">
+        <v>108</v>
+      </c>
+      <c r="F28" t="s">
+        <v>137</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28" t="s">
+        <v>140</v>
+      </c>
+      <c r="L28">
+        <v>4.1</v>
+      </c>
+      <c r="M28">
+        <v>3.4</v>
+      </c>
+      <c r="N28">
+        <v>1.73</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>1.5</v>
+      </c>
+      <c r="S28">
+        <v>2.4</v>
+      </c>
+      <c r="T28">
+        <v>3.28</v>
+      </c>
+      <c r="U28">
+        <v>1.29</v>
+      </c>
+      <c r="V28">
+        <v>8.5</v>
+      </c>
+      <c r="W28">
+        <v>1.04</v>
+      </c>
+      <c r="X28">
+        <v>1.07</v>
+      </c>
+      <c r="Y28">
+        <v>7</v>
+      </c>
+      <c r="Z28">
+        <v>1.42</v>
+      </c>
+      <c r="AA28">
+        <v>2.62</v>
+      </c>
+      <c r="AB28">
+        <v>2.03</v>
+      </c>
+      <c r="AC28">
+        <v>1.69</v>
+      </c>
+      <c r="AD28">
+        <v>4</v>
+      </c>
+      <c r="AE28">
+        <v>1.2</v>
+      </c>
+      <c r="AF28">
+        <v>1.95</v>
+      </c>
+      <c r="AG28">
+        <v>1.73</v>
+      </c>
+      <c r="AH28">
+        <v>8.5</v>
+      </c>
+      <c r="AI28">
+        <v>1.04</v>
+      </c>
+      <c r="AJ28" t="s">
+        <v>141</v>
+      </c>
+      <c r="AK28" t="s">
+        <v>141</v>
+      </c>
+      <c r="AL28">
+        <v>1.23</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+      <c r="AN28">
+        <v>1.33</v>
+      </c>
+      <c r="AO28">
+        <v>-1</v>
+      </c>
+      <c r="AP28">
+        <v>0</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28">
+        <v>0</v>
+      </c>
+      <c r="AV28">
+        <v>0</v>
+      </c>
+      <c r="AW28">
+        <v>0</v>
+      </c>
+      <c r="AX28">
+        <v>0</v>
+      </c>
+      <c r="AY28">
+        <v>0</v>
+      </c>
+      <c r="AZ28">
+        <v>0</v>
+      </c>
+      <c r="BA28">
+        <v>0</v>
+      </c>
+      <c r="BB28">
+        <v>0</v>
+      </c>
+      <c r="BC28">
+        <v>0</v>
+      </c>
+      <c r="BD28" s="3">
+        <v>45828.875</v>
+      </c>
+    </row>
+    <row r="29" spans="1:56">
+      <c r="A29" s="2">
+        <v>45828</v>
+      </c>
+      <c r="B29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" t="s">
+        <v>80</v>
+      </c>
+      <c r="D29" t="s">
+        <v>81</v>
+      </c>
+      <c r="E29" t="s">
+        <v>109</v>
+      </c>
+      <c r="F29" t="s">
+        <v>138</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29">
+        <v>0</v>
+      </c>
+      <c r="AI29">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="s">
+        <v>141</v>
+      </c>
+      <c r="AK29" t="s">
+        <v>141</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+      <c r="AN29">
+        <v>0</v>
+      </c>
+      <c r="AO29">
+        <v>-1</v>
+      </c>
+      <c r="AP29">
+        <v>0</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29">
+        <v>0</v>
+      </c>
+      <c r="AV29">
+        <v>0</v>
+      </c>
+      <c r="AW29">
+        <v>0</v>
+      </c>
+      <c r="AX29">
+        <v>0</v>
+      </c>
+      <c r="AY29">
+        <v>0</v>
+      </c>
+      <c r="AZ29">
+        <v>0</v>
+      </c>
+      <c r="BA29">
+        <v>0</v>
+      </c>
+      <c r="BB29">
+        <v>0</v>
+      </c>
+      <c r="BC29">
+        <v>0</v>
+      </c>
+      <c r="BD29" s="3">
+        <v>45828.875</v>
+      </c>
+    </row>
+    <row r="30" spans="1:56">
+      <c r="A30" s="2">
+        <v>45828</v>
+      </c>
+      <c r="B30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" t="s">
+        <v>77</v>
+      </c>
+      <c r="D30" t="s">
+        <v>81</v>
+      </c>
+      <c r="E30" t="s">
+        <v>110</v>
+      </c>
+      <c r="F30" t="s">
+        <v>139</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" t="s">
+        <v>140</v>
+      </c>
+      <c r="L30">
+        <v>1.81</v>
+      </c>
+      <c r="M30">
+        <v>3.05</v>
+      </c>
+      <c r="N30">
+        <v>4.2</v>
+      </c>
+      <c r="O30">
+        <v>1.5</v>
+      </c>
+      <c r="P30">
+        <v>7</v>
+      </c>
+      <c r="Q30">
+        <v>3.1</v>
+      </c>
+      <c r="R30">
+        <v>1.47</v>
+      </c>
+      <c r="S30">
+        <v>2.4</v>
+      </c>
+      <c r="T30">
+        <v>3.1</v>
+      </c>
+      <c r="U30">
+        <v>1.3</v>
+      </c>
+      <c r="V30">
+        <v>9</v>
+      </c>
+      <c r="W30">
+        <v>1.06</v>
+      </c>
+      <c r="X30">
+        <v>1.05</v>
+      </c>
+      <c r="Y30">
+        <v>8.5</v>
+      </c>
+      <c r="Z30">
+        <v>1.38</v>
+      </c>
+      <c r="AA30">
+        <v>2.75</v>
+      </c>
+      <c r="AB30">
+        <v>2.2</v>
+      </c>
+      <c r="AC30">
+        <v>1.55</v>
+      </c>
+      <c r="AD30">
+        <v>4.33</v>
+      </c>
+      <c r="AE30">
+        <v>1.17</v>
+      </c>
+      <c r="AF30">
+        <v>2.05</v>
+      </c>
+      <c r="AG30">
+        <v>1.7</v>
+      </c>
+      <c r="AH30">
+        <v>8.5</v>
+      </c>
+      <c r="AI30">
+        <v>1.02</v>
+      </c>
+      <c r="AJ30" t="s">
+        <v>141</v>
+      </c>
+      <c r="AK30" t="s">
+        <v>141</v>
+      </c>
+      <c r="AL30">
+        <v>1.33</v>
+      </c>
+      <c r="AM30">
+        <v>1.31</v>
+      </c>
+      <c r="AN30">
+        <v>1.91</v>
+      </c>
+      <c r="AO30">
+        <v>-1</v>
+      </c>
+      <c r="AP30">
         <v>1.24</v>
       </c>
-      <c r="AQ27">
+      <c r="AQ30">
         <v>1.3</v>
       </c>
-      <c r="AR27">
-        <v>1.54</v>
-      </c>
-      <c r="AS27">
+      <c r="AR30">
+        <v>1.67</v>
+      </c>
+      <c r="AS30">
+        <v>1.87</v>
+      </c>
+      <c r="AT30">
+        <v>2.34</v>
+      </c>
+      <c r="AU30">
+        <v>4.35</v>
+      </c>
+      <c r="AV30">
+        <v>3.07</v>
+      </c>
+      <c r="AW30">
         <v>2.05</v>
       </c>
-      <c r="AT27">
-        <v>2.55</v>
-      </c>
-      <c r="AU27">
-        <v>3.65</v>
-      </c>
-      <c r="AV27">
-        <v>3.07</v>
-      </c>
-      <c r="AW27">
-        <v>2.05</v>
-      </c>
-      <c r="AX27">
+      <c r="AX30">
         <v>1.87</v>
       </c>
-      <c r="AY27">
-        <v>1.43</v>
-      </c>
-      <c r="AZ27">
-        <v>0</v>
-      </c>
-      <c r="BA27">
-        <v>0</v>
-      </c>
-      <c r="BB27">
+      <c r="AY30">
+        <v>1.56</v>
+      </c>
+      <c r="AZ30">
+        <v>0</v>
+      </c>
+      <c r="BA30">
+        <v>0</v>
+      </c>
+      <c r="BB30">
         <v>1.5</v>
       </c>
-      <c r="BC27">
+      <c r="BC30">
         <v>3.1</v>
       </c>
-      <c r="BD27" s="3">
+      <c r="BD30" s="3">
         <v>45828.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-06-20.xlsx
+++ b/jogos_2025-06-20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="153">
   <si>
     <t>Date</t>
   </si>
@@ -190,6 +190,9 @@
     <t>12:00</t>
   </si>
   <si>
+    <t>13:00</t>
+  </si>
+  <si>
     <t>13:30</t>
   </si>
   <si>
@@ -229,15 +232,18 @@
     <t>Belarus Vysheyshaya Liga</t>
   </si>
   <si>
+    <t>Algeria Ligue 1</t>
+  </si>
+  <si>
     <t>Chile Primera B</t>
   </si>
   <si>
+    <t>Republic of Ireland Premier Division</t>
+  </si>
+  <si>
     <t>Republic of Ireland First Division</t>
   </si>
   <si>
-    <t>Republic of Ireland Premier Division</t>
-  </si>
-  <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
@@ -253,25 +259,34 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>USA NWSL</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>2025</t>
   </si>
   <si>
+    <t>2024/2025</t>
+  </si>
+  <si>
     <t>Sydney II</t>
   </si>
   <si>
+    <t>Neftchi</t>
+  </si>
+  <si>
+    <t>Smorgon</t>
+  </si>
+  <si>
     <t>Mash'al</t>
   </si>
   <si>
-    <t>Smorgon</t>
-  </si>
-  <si>
-    <t>Neftchi</t>
+    <t>USM Khenchela</t>
+  </si>
+  <si>
+    <t>ES Sétif</t>
   </si>
   <si>
     <t>Unión San Felipe</t>
@@ -280,45 +295,51 @@
     <t>Slavia</t>
   </si>
   <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
+    <t>MC Oran</t>
+  </si>
+  <si>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
     <t>UCD</t>
   </si>
   <si>
-    <t>Wexford</t>
+    <t>Waterford</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
   </si>
   <si>
     <t>Shamrock Rovers</t>
   </si>
   <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Waterford</t>
-  </si>
-  <si>
-    <t>Kerry</t>
-  </si>
-  <si>
     <t>Racing Córdoba</t>
   </si>
   <si>
+    <t>Recoleta</t>
+  </si>
+  <si>
     <t>Cobreloa</t>
   </si>
   <si>
-    <t>Recoleta</t>
-  </si>
-  <si>
     <t>Unión La Calera</t>
   </si>
   <si>
@@ -337,28 +358,34 @@
     <t>Hartford Athletic</t>
   </si>
   <si>
+    <t>Huntsville City</t>
+  </si>
+  <si>
     <t>Kansas City</t>
   </si>
   <si>
     <t>Racing Louisville</t>
   </si>
   <si>
-    <t>Huntsville City</t>
-  </si>
-  <si>
     <t>América Mineiro</t>
   </si>
   <si>
     <t>APIA Leichhardt Tigers</t>
   </si>
   <si>
+    <t>Buxoro</t>
+  </si>
+  <si>
+    <t>Isloch</t>
+  </si>
+  <si>
     <t>Nasaf</t>
   </si>
   <si>
-    <t>Isloch</t>
-  </si>
-  <si>
-    <t>Buxoro</t>
+    <t>El Bayadh</t>
+  </si>
+  <si>
+    <t>US Biskra</t>
   </si>
   <si>
     <t>Concepción</t>
@@ -367,45 +394,51 @@
     <t>BATE</t>
   </si>
   <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
+    <t>St Patrick's Athl.</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
     <t>Cobh Ramblers</t>
   </si>
   <si>
-    <t>Longford Town</t>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Sligo Rovers</t>
   </si>
   <si>
     <t>Cork City</t>
   </si>
   <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Derry City</t>
-  </si>
-  <si>
-    <t>St Patrick's Athl.</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
     <t>Deportivo Madryn</t>
   </si>
   <si>
+    <t>Deportes Temuco</t>
+  </si>
+  <si>
     <t>Curicó Unido</t>
   </si>
   <si>
-    <t>Deportes Temuco</t>
-  </si>
-  <si>
     <t>Universidad Católica</t>
   </si>
   <si>
@@ -424,13 +457,13 @@
     <t>Loudoun United</t>
   </si>
   <si>
+    <t>Crown Legacy</t>
+  </si>
+  <si>
     <t>Angel City</t>
   </si>
   <si>
     <t>Orlando Pride</t>
-  </si>
-  <si>
-    <t>Crown Legacy</t>
   </si>
   <si>
     <t>Criciúma</t>
@@ -803,7 +836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD30"/>
+  <dimension ref="A1:BD34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:56">
@@ -984,16 +1017,16 @@
         <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1008,16 +1041,16 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L2">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="M2">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="N2">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="O2">
         <v>2.75</v>
@@ -1029,73 +1062,73 @@
         <v>1.44</v>
       </c>
       <c r="R2">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="S2">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="T2">
-        <v>2.28</v>
+        <v>1.93</v>
       </c>
       <c r="U2">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="V2">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="W2">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="X2">
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="Z2">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AA2">
-        <v>4.45</v>
+        <v>5.8</v>
       </c>
       <c r="AB2">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="AC2">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD2">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="AE2">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AF2">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AG2">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AH2">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="AI2">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="AJ2" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AK2" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AL2">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AM2">
         <v>1.17</v>
       </c>
       <c r="AN2">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AO2">
         <v>-1</v>
@@ -1154,16 +1187,16 @@
         <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1178,94 +1211,94 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ3" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AK3" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AM3">
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AO3">
         <v>-1</v>
@@ -1307,10 +1340,10 @@
         <v>0</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BC3">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BD3" s="3">
         <v>45828.5</v>
@@ -1324,16 +1357,16 @@
         <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F4" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1348,16 +1381,16 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L4">
-        <v>4.49</v>
+        <v>5.1</v>
       </c>
       <c r="M4">
-        <v>3.75</v>
+        <v>3.52</v>
       </c>
       <c r="N4">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -1411,10 +1444,10 @@
         <v>1.25</v>
       </c>
       <c r="AF4">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AG4">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AH4">
         <v>6.55</v>
@@ -1423,19 +1456,19 @@
         <v>1.05</v>
       </c>
       <c r="AJ4" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AK4" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AL4">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AM4">
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AO4">
         <v>-1</v>
@@ -1494,16 +1527,16 @@
         <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F5" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1518,94 +1551,94 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ5" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AK5" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AM5">
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AO5">
         <v>-1</v>
@@ -1647,10 +1680,10 @@
         <v>0</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BD5" s="3">
         <v>45828.5</v>
@@ -1664,16 +1697,16 @@
         <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F6" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1688,16 +1721,16 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L6">
-        <v>2.54</v>
+        <v>1.96</v>
       </c>
       <c r="M6">
-        <v>3.23</v>
+        <v>3</v>
       </c>
       <c r="N6">
-        <v>2.39</v>
+        <v>4.2</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1733,16 +1766,16 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB6">
-        <v>2.21</v>
+        <v>2.75</v>
       </c>
       <c r="AC6">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1763,10 +1796,10 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AK6" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1823,7 +1856,7 @@
         <v>0</v>
       </c>
       <c r="BD6" s="3">
-        <v>45828.5625</v>
+        <v>45828.54166666666</v>
       </c>
     </row>
     <row r="7" spans="1:56">
@@ -1831,19 +1864,19 @@
         <v>45828</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F7" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1858,16 +1891,16 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L7">
-        <v>1.67</v>
+        <v>1.26</v>
       </c>
       <c r="M7">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="N7">
-        <v>4.72</v>
+        <v>9.35</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -1879,73 +1912,73 @@
         <v>0</v>
       </c>
       <c r="R7">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="Z7">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AC7">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AD7">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="AE7">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AF7">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH7">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AK7" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AL7">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AM7">
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AO7">
         <v>-1</v>
@@ -1993,7 +2026,7 @@
         <v>0</v>
       </c>
       <c r="BD7" s="3">
-        <v>45828.58333333334</v>
+        <v>45828.54166666666</v>
       </c>
     </row>
     <row r="8" spans="1:56">
@@ -2001,19 +2034,19 @@
         <v>45828</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F8" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2028,85 +2061,85 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L8">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="M8">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="N8">
-        <v>2.27</v>
+        <v>2.78</v>
       </c>
       <c r="O8">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="P8">
-        <v>9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q8">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="R8">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S8">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="T8">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="U8">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W8">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
         <v>1.06</v>
       </c>
       <c r="Y8">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z8">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AA8">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="AB8">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AC8">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AD8">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="AE8">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AF8">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG8">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH8">
-        <v>6.1</v>
+        <v>8</v>
       </c>
       <c r="AI8">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AJ8" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AK8" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AL8">
         <v>1.33</v>
@@ -2115,7 +2148,7 @@
         <v>1.28</v>
       </c>
       <c r="AN8">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AO8">
         <v>-1</v>
@@ -2157,13 +2190,13 @@
         <v>0</v>
       </c>
       <c r="BB8">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="BC8">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="BD8" s="3">
-        <v>45828.65625</v>
+        <v>45828.5625</v>
       </c>
     </row>
     <row r="9" spans="1:56">
@@ -2174,16 +2207,16 @@
         <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F9" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2198,94 +2231,94 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L9">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="M9">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="N9">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="O9">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S9">
-        <v>3.1</v>
+        <v>2.71</v>
       </c>
       <c r="T9">
-        <v>2.35</v>
+        <v>2.67</v>
       </c>
       <c r="U9">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="V9">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="W9">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="Z9">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AA9">
-        <v>4.2</v>
+        <v>3.32</v>
       </c>
       <c r="AB9">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AC9">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AD9">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="AE9">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AF9">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="AG9">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AH9">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AI9">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AJ9" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AK9" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AL9">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AM9">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN9">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AO9">
         <v>-1</v>
@@ -2327,13 +2360,13 @@
         <v>0</v>
       </c>
       <c r="BB9">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BC9">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BD9" s="3">
-        <v>45828.65625</v>
+        <v>45828.58333333334</v>
       </c>
     </row>
     <row r="10" spans="1:56">
@@ -2344,16 +2377,16 @@
         <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F10" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2368,127 +2401,127 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L10">
-        <v>1.38</v>
+        <v>1.84</v>
       </c>
       <c r="M10">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="N10">
-        <v>6.6</v>
+        <v>4.05</v>
       </c>
       <c r="O10">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AA10">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="AB10">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="AC10">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AD10">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH10">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AK10" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AL10">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN10">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AO10">
         <v>-1</v>
       </c>
       <c r="AP10">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ10">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AR10">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AU10">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AV10">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AW10">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AX10">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AY10">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ10">
         <v>0</v>
@@ -2497,13 +2530,13 @@
         <v>0</v>
       </c>
       <c r="BB10">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BD10" s="3">
-        <v>45828.65625</v>
+        <v>45828.58333333334</v>
       </c>
     </row>
     <row r="11" spans="1:56">
@@ -2514,16 +2547,16 @@
         <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F11" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2538,127 +2571,127 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L11">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="M11">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="N11">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
         <v>1.5</v>
       </c>
-      <c r="P11">
-        <v>13</v>
-      </c>
-      <c r="Q11">
-        <v>2.88</v>
-      </c>
-      <c r="R11">
-        <v>1.33</v>
-      </c>
-      <c r="S11">
-        <v>3</v>
-      </c>
-      <c r="T11">
-        <v>2.65</v>
-      </c>
-      <c r="U11">
-        <v>1.42</v>
-      </c>
-      <c r="V11">
-        <v>6.5</v>
-      </c>
-      <c r="W11">
-        <v>1.1</v>
-      </c>
-      <c r="X11">
-        <v>1.05</v>
-      </c>
-      <c r="Y11">
-        <v>9.5</v>
-      </c>
-      <c r="Z11">
-        <v>1.25</v>
-      </c>
       <c r="AA11">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="AB11">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="AC11">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AD11">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH11">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AI11">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AK11" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AL11">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AM11">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN11">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AO11">
         <v>-1</v>
       </c>
       <c r="AP11">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ11">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR11">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AS11">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AT11">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AU11">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AV11">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AW11">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AX11">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY11">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ11">
         <v>0</v>
@@ -2667,13 +2700,13 @@
         <v>0</v>
       </c>
       <c r="BB11">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BC11">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BD11" s="3">
-        <v>45828.65625</v>
+        <v>45828.58333333334</v>
       </c>
     </row>
     <row r="12" spans="1:56">
@@ -2681,19 +2714,19 @@
         <v>45828</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E12" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F12" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2708,127 +2741,127 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L12">
-        <v>2.02</v>
+        <v>2.72</v>
       </c>
       <c r="M12">
         <v>3.15</v>
       </c>
       <c r="N12">
-        <v>3.26</v>
+        <v>2.6</v>
       </c>
       <c r="O12">
-        <v>1.69</v>
+        <v>2.1</v>
       </c>
       <c r="P12">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="Q12">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="R12">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="S12">
+        <v>2.5</v>
+      </c>
+      <c r="T12">
         <v>2.9</v>
       </c>
-      <c r="T12">
-        <v>2.8</v>
-      </c>
       <c r="U12">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
         <v>1.06</v>
       </c>
       <c r="Y12">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z12">
         <v>1.3</v>
       </c>
       <c r="AA12">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AB12">
+        <v>2.07</v>
+      </c>
+      <c r="AC12">
+        <v>1.67</v>
+      </c>
+      <c r="AD12">
+        <v>3.55</v>
+      </c>
+      <c r="AE12">
+        <v>1.22</v>
+      </c>
+      <c r="AF12">
+        <v>1.73</v>
+      </c>
+      <c r="AG12">
         <v>1.95</v>
       </c>
-      <c r="AC12">
-        <v>1.75</v>
-      </c>
-      <c r="AD12">
-        <v>3.3</v>
-      </c>
-      <c r="AE12">
-        <v>1.25</v>
-      </c>
-      <c r="AF12">
-        <v>1.67</v>
-      </c>
-      <c r="AG12">
-        <v>2</v>
-      </c>
       <c r="AH12">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
       <c r="AI12">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AJ12" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AK12" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AL12">
         <v>1.33</v>
       </c>
       <c r="AM12">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AN12">
-        <v>1.73</v>
+        <v>1.37</v>
       </c>
       <c r="AO12">
         <v>-1</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ12">
         <v>0</v>
@@ -2837,10 +2870,10 @@
         <v>0</v>
       </c>
       <c r="BB12">
-        <v>1.69</v>
+        <v>2.1</v>
       </c>
       <c r="BC12">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="BD12" s="3">
         <v>45828.65625</v>
@@ -2851,19 +2884,19 @@
         <v>45828</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E13" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F13" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2878,139 +2911,139 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L13">
-        <v>2.29</v>
+        <v>1.57</v>
       </c>
       <c r="M13">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="N13">
-        <v>2.97</v>
+        <v>4.85</v>
       </c>
       <c r="O13">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="P13">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="Q13">
+        <v>2.8</v>
+      </c>
+      <c r="R13">
+        <v>1.3</v>
+      </c>
+      <c r="S13">
+        <v>3.1</v>
+      </c>
+      <c r="T13">
+        <v>2.3</v>
+      </c>
+      <c r="U13">
+        <v>1.52</v>
+      </c>
+      <c r="V13">
+        <v>5.2</v>
+      </c>
+      <c r="W13">
+        <v>1.11</v>
+      </c>
+      <c r="X13">
+        <v>1.03</v>
+      </c>
+      <c r="Y13">
+        <v>13</v>
+      </c>
+      <c r="Z13">
+        <v>1.16</v>
+      </c>
+      <c r="AA13">
+        <v>4.2</v>
+      </c>
+      <c r="AB13">
+        <v>1.67</v>
+      </c>
+      <c r="AC13">
+        <v>2.15</v>
+      </c>
+      <c r="AD13">
+        <v>2.7</v>
+      </c>
+      <c r="AE13">
+        <v>1.44</v>
+      </c>
+      <c r="AF13">
+        <v>1.67</v>
+      </c>
+      <c r="AG13">
+        <v>2.1</v>
+      </c>
+      <c r="AH13">
+        <v>4.8</v>
+      </c>
+      <c r="AI13">
+        <v>1.17</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>152</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>152</v>
+      </c>
+      <c r="AL13">
+        <v>1.25</v>
+      </c>
+      <c r="AM13">
+        <v>1.18</v>
+      </c>
+      <c r="AN13">
         <v>2.25</v>
-      </c>
-      <c r="R13">
-        <v>1.52</v>
-      </c>
-      <c r="S13">
-        <v>2.35</v>
-      </c>
-      <c r="T13">
-        <v>3.42</v>
-      </c>
-      <c r="U13">
-        <v>1.23</v>
-      </c>
-      <c r="V13">
-        <v>8.9</v>
-      </c>
-      <c r="W13">
-        <v>1.01</v>
-      </c>
-      <c r="X13">
-        <v>1.06</v>
-      </c>
-      <c r="Y13">
-        <v>6</v>
-      </c>
-      <c r="Z13">
-        <v>1.41</v>
-      </c>
-      <c r="AA13">
-        <v>2.65</v>
-      </c>
-      <c r="AB13">
-        <v>2.3</v>
-      </c>
-      <c r="AC13">
-        <v>1.5</v>
-      </c>
-      <c r="AD13">
-        <v>4.9</v>
-      </c>
-      <c r="AE13">
-        <v>1.13</v>
-      </c>
-      <c r="AF13">
-        <v>2.1</v>
-      </c>
-      <c r="AG13">
-        <v>1.65</v>
-      </c>
-      <c r="AH13">
-        <v>9.1</v>
-      </c>
-      <c r="AI13">
-        <v>1.05</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>141</v>
-      </c>
-      <c r="AK13" t="s">
-        <v>141</v>
-      </c>
-      <c r="AL13">
-        <v>1.36</v>
-      </c>
-      <c r="AM13">
-        <v>1.36</v>
-      </c>
-      <c r="AN13">
-        <v>1.44</v>
       </c>
       <c r="AO13">
         <v>-1</v>
       </c>
       <c r="AP13">
+        <v>1.36</v>
+      </c>
+      <c r="AQ13">
+        <v>1.57</v>
+      </c>
+      <c r="AR13">
+        <v>2.28</v>
+      </c>
+      <c r="AS13">
+        <v>2.5</v>
+      </c>
+      <c r="AT13">
+        <v>3.3</v>
+      </c>
+      <c r="AU13">
+        <v>2.9</v>
+      </c>
+      <c r="AV13">
+        <v>2.25</v>
+      </c>
+      <c r="AW13">
+        <v>1.75</v>
+      </c>
+      <c r="AX13">
+        <v>1.48</v>
+      </c>
+      <c r="AY13">
+        <v>1.29</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
         <v>1.5</v>
       </c>
-      <c r="AQ13">
-        <v>1.85</v>
-      </c>
-      <c r="AR13">
-        <v>2.35</v>
-      </c>
-      <c r="AS13">
-        <v>3.15</v>
-      </c>
-      <c r="AT13">
-        <v>4.1</v>
-      </c>
-      <c r="AU13">
-        <v>2.45</v>
-      </c>
-      <c r="AV13">
-        <v>1.81</v>
-      </c>
-      <c r="AW13">
-        <v>1.5</v>
-      </c>
-      <c r="AX13">
-        <v>1.29</v>
-      </c>
-      <c r="AY13">
-        <v>1.18</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>1.91</v>
-      </c>
       <c r="BC13">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="BD13" s="3">
         <v>45828.65625</v>
@@ -3021,19 +3054,19 @@
         <v>45828</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F14" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -3048,40 +3081,40 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L14">
-        <v>2.57</v>
+        <v>1.95</v>
       </c>
       <c r="M14">
-        <v>3.07</v>
+        <v>3.3</v>
       </c>
       <c r="N14">
-        <v>2.47</v>
+        <v>3.3</v>
       </c>
       <c r="O14">
-        <v>2.1</v>
+        <v>1.69</v>
       </c>
       <c r="P14">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="Q14">
-        <v>1.91</v>
+        <v>2.28</v>
       </c>
       <c r="R14">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S14">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T14">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="U14">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V14">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="W14">
         <v>1.07</v>
@@ -3090,85 +3123,85 @@
         <v>1.06</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="Z14">
         <v>1.3</v>
       </c>
       <c r="AA14">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AB14">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC14">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AD14">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AE14">
         <v>1.25</v>
       </c>
       <c r="AF14">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AG14">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI14">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AJ14" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AK14" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AL14">
         <v>1.33</v>
       </c>
       <c r="AM14">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AN14">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AO14">
         <v>-1</v>
       </c>
       <c r="AP14">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AQ14">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AR14">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AS14">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AT14">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AU14">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="AV14">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AW14">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AX14">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AY14">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AZ14">
         <v>0</v>
@@ -3177,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="BB14">
-        <v>2.1</v>
+        <v>1.69</v>
       </c>
       <c r="BC14">
-        <v>1.91</v>
+        <v>2.28</v>
       </c>
       <c r="BD14" s="3">
         <v>45828.65625</v>
@@ -3191,19 +3224,19 @@
         <v>45828</v>
       </c>
       <c r="B15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E15" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F15" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3218,127 +3251,127 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L15">
-        <v>1.37</v>
+        <v>2.5</v>
       </c>
       <c r="M15">
-        <v>4.2</v>
+        <v>2.91</v>
       </c>
       <c r="N15">
+        <v>2.9</v>
+      </c>
+      <c r="O15">
+        <v>1.91</v>
+      </c>
+      <c r="P15">
         <v>6.4</v>
       </c>
-      <c r="O15">
-        <v>1.34</v>
-      </c>
-      <c r="P15">
-        <v>13</v>
-      </c>
       <c r="Q15">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="R15">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="S15">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="T15">
-        <v>2.54</v>
+        <v>3.5</v>
       </c>
       <c r="U15">
+        <v>1.25</v>
+      </c>
+      <c r="V15">
+        <v>8.5</v>
+      </c>
+      <c r="W15">
+        <v>1.04</v>
+      </c>
+      <c r="X15">
+        <v>1.09</v>
+      </c>
+      <c r="Y15">
+        <v>5.8</v>
+      </c>
+      <c r="Z15">
         <v>1.5</v>
       </c>
-      <c r="V15">
+      <c r="AA15">
+        <v>2.36</v>
+      </c>
+      <c r="AB15">
+        <v>2.45</v>
+      </c>
+      <c r="AC15">
+        <v>1.44</v>
+      </c>
+      <c r="AD15">
         <v>5</v>
       </c>
-      <c r="W15">
-        <v>1.12</v>
-      </c>
-      <c r="X15">
+      <c r="AE15">
+        <v>1.13</v>
+      </c>
+      <c r="AF15">
+        <v>2</v>
+      </c>
+      <c r="AG15">
+        <v>1.7</v>
+      </c>
+      <c r="AH15">
+        <v>9.1</v>
+      </c>
+      <c r="AI15">
         <v>1.04</v>
       </c>
-      <c r="Y15">
-        <v>11</v>
-      </c>
-      <c r="Z15">
-        <v>1.22</v>
-      </c>
-      <c r="AA15">
-        <v>4</v>
-      </c>
-      <c r="AB15">
-        <v>1.67</v>
-      </c>
-      <c r="AC15">
-        <v>2</v>
-      </c>
-      <c r="AD15">
-        <v>2.23</v>
-      </c>
-      <c r="AE15">
-        <v>1.54</v>
-      </c>
-      <c r="AF15">
-        <v>1.9</v>
-      </c>
-      <c r="AG15">
-        <v>1.8</v>
-      </c>
-      <c r="AH15">
-        <v>4.5</v>
-      </c>
-      <c r="AI15">
-        <v>1.15</v>
-      </c>
       <c r="AJ15" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AK15" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AL15">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AM15">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AN15">
-        <v>2.8</v>
+        <v>1.44</v>
       </c>
       <c r="AO15">
         <v>-1</v>
       </c>
       <c r="AP15">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AU15">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AV15">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AW15">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AX15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AY15">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ15">
         <v>0</v>
@@ -3347,10 +3380,10 @@
         <v>0</v>
       </c>
       <c r="BB15">
-        <v>1.34</v>
+        <v>1.91</v>
       </c>
       <c r="BC15">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="BD15" s="3">
         <v>45828.65625</v>
@@ -3361,19 +3394,19 @@
         <v>45828</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E16" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F16" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3388,127 +3421,127 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L16">
-        <v>3.82</v>
+        <v>2.9</v>
       </c>
       <c r="M16">
-        <v>3.47</v>
+        <v>3.55</v>
       </c>
       <c r="N16">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="O16">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="P16">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="R16">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S16">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
       <c r="T16">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="U16">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V16">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W16">
         <v>1.09</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AA16">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AB16">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AC16">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AD16">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="AE16">
+        <v>1.4</v>
+      </c>
+      <c r="AF16">
+        <v>1.55</v>
+      </c>
+      <c r="AG16">
+        <v>2.25</v>
+      </c>
+      <c r="AH16">
+        <v>4.94</v>
+      </c>
+      <c r="AI16">
+        <v>1.15</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>152</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>152</v>
+      </c>
+      <c r="AL16">
+        <v>1.3</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
         <v>1.36</v>
-      </c>
-      <c r="AF16">
-        <v>1.76</v>
-      </c>
-      <c r="AG16">
-        <v>1.95</v>
-      </c>
-      <c r="AH16">
-        <v>5.92</v>
-      </c>
-      <c r="AI16">
-        <v>1.12</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>141</v>
-      </c>
-      <c r="AK16" t="s">
-        <v>141</v>
-      </c>
-      <c r="AL16">
-        <v>1.25</v>
-      </c>
-      <c r="AM16">
-        <v>1.26</v>
-      </c>
-      <c r="AN16">
-        <v>1.22</v>
       </c>
       <c r="AO16">
         <v>-1</v>
       </c>
       <c r="AP16">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AQ16">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR16">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AS16">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="AT16">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="AU16">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AV16">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="AW16">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="AX16">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AY16">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AZ16">
         <v>0</v>
@@ -3517,10 +3550,10 @@
         <v>0</v>
       </c>
       <c r="BB16">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="BC16">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="BD16" s="3">
         <v>45828.65625</v>
@@ -3531,19 +3564,19 @@
         <v>45828</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E17" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F17" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3558,127 +3591,127 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L17">
-        <v>3.02</v>
+        <v>1.39</v>
       </c>
       <c r="M17">
-        <v>3.41</v>
+        <v>4.5</v>
       </c>
       <c r="N17">
-        <v>2.02</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>2.38</v>
+        <v>1.34</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q17">
-        <v>1.62</v>
+        <v>3.4</v>
       </c>
       <c r="R17">
         <v>1.31</v>
       </c>
       <c r="S17">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="T17">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="U17">
+        <v>1.5</v>
+      </c>
+      <c r="V17">
+        <v>5.2</v>
+      </c>
+      <c r="W17">
+        <v>1.11</v>
+      </c>
+      <c r="X17">
+        <v>1.01</v>
+      </c>
+      <c r="Y17">
+        <v>11.4</v>
+      </c>
+      <c r="Z17">
+        <v>1.17</v>
+      </c>
+      <c r="AA17">
+        <v>3.84</v>
+      </c>
+      <c r="AB17">
+        <v>1.68</v>
+      </c>
+      <c r="AC17">
+        <v>2.1</v>
+      </c>
+      <c r="AD17">
+        <v>2.7</v>
+      </c>
+      <c r="AE17">
         <v>1.42</v>
       </c>
-      <c r="V17">
-        <v>5.5</v>
-      </c>
-      <c r="W17">
-        <v>1.09</v>
-      </c>
-      <c r="X17">
-        <v>1.05</v>
-      </c>
-      <c r="Y17">
-        <v>11</v>
-      </c>
-      <c r="Z17">
-        <v>1.25</v>
-      </c>
-      <c r="AA17">
-        <v>3.8</v>
-      </c>
-      <c r="AB17">
-        <v>1.7</v>
-      </c>
-      <c r="AC17">
-        <v>1.95</v>
-      </c>
-      <c r="AD17">
-        <v>3</v>
-      </c>
-      <c r="AE17">
-        <v>1.36</v>
-      </c>
       <c r="AF17">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG17">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AH17">
-        <v>5.5</v>
+        <v>5.04</v>
       </c>
       <c r="AI17">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AJ17" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AK17" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AL17">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN17">
-        <v>1.33</v>
+        <v>2.8</v>
       </c>
       <c r="AO17">
         <v>-1</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AU17">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AW17">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AX17">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AY17">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ17">
         <v>0</v>
@@ -3687,10 +3720,10 @@
         <v>0</v>
       </c>
       <c r="BB17">
-        <v>2.38</v>
+        <v>1.34</v>
       </c>
       <c r="BC17">
-        <v>1.62</v>
+        <v>3.4</v>
       </c>
       <c r="BD17" s="3">
         <v>45828.65625</v>
@@ -3704,16 +3737,16 @@
         <v>61</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E18" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F18" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -3728,127 +3761,127 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L18">
-        <v>2.05</v>
+        <v>2.81</v>
       </c>
       <c r="M18">
-        <v>2.79</v>
+        <v>3.34</v>
       </c>
       <c r="N18">
-        <v>3.67</v>
+        <v>2.3</v>
       </c>
       <c r="O18">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="P18">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="Q18">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="R18">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="S18">
+        <v>2.65</v>
+      </c>
+      <c r="T18">
+        <v>2.6</v>
+      </c>
+      <c r="U18">
+        <v>1.4</v>
+      </c>
+      <c r="V18">
+        <v>6</v>
+      </c>
+      <c r="W18">
+        <v>1.08</v>
+      </c>
+      <c r="X18">
+        <v>1.01</v>
+      </c>
+      <c r="Y18">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="Z18">
+        <v>1.25</v>
+      </c>
+      <c r="AA18">
+        <v>3.3</v>
+      </c>
+      <c r="AB18">
+        <v>1.95</v>
+      </c>
+      <c r="AC18">
+        <v>1.86</v>
+      </c>
+      <c r="AD18">
+        <v>3.14</v>
+      </c>
+      <c r="AE18">
+        <v>1.27</v>
+      </c>
+      <c r="AF18">
+        <v>1.75</v>
+      </c>
+      <c r="AG18">
         <v>2</v>
       </c>
-      <c r="T18">
-        <v>4.33</v>
-      </c>
-      <c r="U18">
-        <v>1.17</v>
-      </c>
-      <c r="V18">
-        <v>11</v>
-      </c>
-      <c r="W18">
-        <v>1.02</v>
-      </c>
-      <c r="X18">
-        <v>1.13</v>
-      </c>
-      <c r="Y18">
-        <v>4.75</v>
-      </c>
-      <c r="Z18">
-        <v>1.65</v>
-      </c>
-      <c r="AA18">
-        <v>2.1</v>
-      </c>
-      <c r="AB18">
-        <v>2.3</v>
-      </c>
-      <c r="AC18">
-        <v>1.5</v>
-      </c>
-      <c r="AD18">
-        <v>5.88</v>
-      </c>
-      <c r="AE18">
-        <v>1.11</v>
-      </c>
-      <c r="AF18">
-        <v>2.3</v>
-      </c>
-      <c r="AG18">
-        <v>1.55</v>
-      </c>
       <c r="AH18">
-        <v>14</v>
+        <v>5.92</v>
       </c>
       <c r="AI18">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AJ18" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AK18" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AL18">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AM18">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AN18">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AO18">
         <v>-1</v>
       </c>
       <c r="AP18">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU18">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AV18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW18">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AX18">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ18">
         <v>0</v>
@@ -3857,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="BB18">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="BC18">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="BD18" s="3">
-        <v>45828.66666666666</v>
+        <v>45828.65625</v>
       </c>
     </row>
     <row r="19" spans="1:56">
@@ -3874,16 +3907,16 @@
         <v>61</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E19" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F19" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -3898,127 +3931,127 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L19">
-        <v>1.63</v>
+        <v>4.24</v>
       </c>
       <c r="M19">
-        <v>3.36</v>
+        <v>3.75</v>
       </c>
       <c r="N19">
-        <v>4.8</v>
+        <v>1.75</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB19">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="AC19">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ19" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AK19" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO19">
         <v>-1</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AU19">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AV19">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX19">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AY19">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AZ19">
         <v>0</v>
@@ -4027,13 +4060,13 @@
         <v>0</v>
       </c>
       <c r="BB19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BC19">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BD19" s="3">
-        <v>45828.66666666666</v>
+        <v>45828.65625</v>
       </c>
     </row>
     <row r="20" spans="1:56">
@@ -4044,16 +4077,16 @@
         <v>61</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E20" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F20" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -4068,127 +4101,127 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L20">
-        <v>2.11</v>
+        <v>1.73</v>
       </c>
       <c r="M20">
-        <v>3.17</v>
+        <v>3.65</v>
       </c>
       <c r="N20">
-        <v>3.03</v>
+        <v>4.35</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB20">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC20">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ20" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AK20" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN20">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO20">
         <v>-1</v>
       </c>
       <c r="AP20">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AU20">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV20">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AW20">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AX20">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AY20">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ20">
         <v>0</v>
@@ -4197,13 +4230,13 @@
         <v>0</v>
       </c>
       <c r="BB20">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BC20">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BD20" s="3">
-        <v>45828.66666666666</v>
+        <v>45828.65625</v>
       </c>
     </row>
     <row r="21" spans="1:56">
@@ -4211,19 +4244,19 @@
         <v>45828</v>
       </c>
       <c r="B21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F21" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -4238,127 +4271,127 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L21">
+        <v>1.25</v>
+      </c>
+      <c r="M21">
+        <v>5.5</v>
+      </c>
+      <c r="N21">
+        <v>8.5</v>
+      </c>
+      <c r="O21">
+        <v>1.18</v>
+      </c>
+      <c r="P21">
+        <v>15</v>
+      </c>
+      <c r="Q21">
+        <v>5</v>
+      </c>
+      <c r="R21">
+        <v>1.29</v>
+      </c>
+      <c r="S21">
+        <v>3.2</v>
+      </c>
+      <c r="T21">
         <v>2.55</v>
       </c>
-      <c r="M21">
-        <v>3.2</v>
-      </c>
-      <c r="N21">
-        <v>2.65</v>
-      </c>
-      <c r="O21">
+      <c r="U21">
+        <v>1.5</v>
+      </c>
+      <c r="V21">
+        <v>5.2</v>
+      </c>
+      <c r="W21">
+        <v>1.12</v>
+      </c>
+      <c r="X21">
+        <v>1.03</v>
+      </c>
+      <c r="Y21">
+        <v>12</v>
+      </c>
+      <c r="Z21">
+        <v>1.23</v>
+      </c>
+      <c r="AA21">
+        <v>3.9</v>
+      </c>
+      <c r="AB21">
+        <v>1.67</v>
+      </c>
+      <c r="AC21">
         <v>2.05</v>
       </c>
-      <c r="P21">
-        <v>8</v>
-      </c>
-      <c r="Q21">
-        <v>2.05</v>
-      </c>
-      <c r="R21">
-        <v>1.48</v>
-      </c>
-      <c r="S21">
-        <v>2.48</v>
-      </c>
-      <c r="T21">
-        <v>3.3</v>
-      </c>
-      <c r="U21">
-        <v>1.29</v>
-      </c>
-      <c r="V21">
-        <v>8</v>
-      </c>
-      <c r="W21">
-        <v>1.04</v>
-      </c>
-      <c r="X21">
-        <v>1.05</v>
-      </c>
-      <c r="Y21">
-        <v>8</v>
-      </c>
-      <c r="Z21">
+      <c r="AD21">
+        <v>3</v>
+      </c>
+      <c r="AE21">
         <v>1.36</v>
       </c>
-      <c r="AA21">
-        <v>2.88</v>
-      </c>
-      <c r="AB21">
-        <v>2.28</v>
-      </c>
-      <c r="AC21">
-        <v>1.58</v>
-      </c>
-      <c r="AD21">
-        <v>4.5</v>
-      </c>
-      <c r="AE21">
-        <v>1.17</v>
-      </c>
       <c r="AF21">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AG21">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AH21">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AI21">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AJ21" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AK21" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AL21">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="AM21">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AN21">
-        <v>1.49</v>
+        <v>3.4</v>
       </c>
       <c r="AO21">
         <v>-1</v>
       </c>
       <c r="AP21">
+        <v>1.22</v>
+      </c>
+      <c r="AQ21">
         <v>1.38</v>
       </c>
-      <c r="AQ21">
+      <c r="AR21">
         <v>1.65</v>
       </c>
-      <c r="AR21">
-        <v>2.06</v>
-      </c>
       <c r="AS21">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="AT21">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="AU21">
-        <v>2.65</v>
+        <v>3.8</v>
       </c>
       <c r="AV21">
-        <v>2.02</v>
+        <v>2.8</v>
       </c>
       <c r="AW21">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="AX21">
-        <v>1.38</v>
+        <v>1.73</v>
       </c>
       <c r="AY21">
-        <v>1.23</v>
+        <v>1.48</v>
       </c>
       <c r="AZ21">
         <v>0</v>
@@ -4367,13 +4400,13 @@
         <v>0</v>
       </c>
       <c r="BB21">
-        <v>2.05</v>
+        <v>1.18</v>
       </c>
       <c r="BC21">
-        <v>2.05</v>
+        <v>5</v>
       </c>
       <c r="BD21" s="3">
-        <v>45828.77083333334</v>
+        <v>45828.65625</v>
       </c>
     </row>
     <row r="22" spans="1:56">
@@ -4381,19 +4414,19 @@
         <v>45828</v>
       </c>
       <c r="B22" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C22" t="s">
         <v>76</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E22" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F22" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -4408,127 +4441,127 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ22" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AK22" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO22">
         <v>-1</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU22">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AV22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW22">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AX22">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY22">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ22">
         <v>0</v>
@@ -4537,13 +4570,13 @@
         <v>0</v>
       </c>
       <c r="BB22">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BC22">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BD22" s="3">
-        <v>45828.79166666666</v>
+        <v>45828.66666666666</v>
       </c>
     </row>
     <row r="23" spans="1:56">
@@ -4551,19 +4584,19 @@
         <v>45828</v>
       </c>
       <c r="B23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C23" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E23" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F23" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -4578,127 +4611,127 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L23">
-        <v>3.14</v>
+        <v>2.1</v>
       </c>
       <c r="M23">
-        <v>2.94</v>
+        <v>3.11</v>
       </c>
       <c r="N23">
-        <v>2.17</v>
+        <v>3.28</v>
       </c>
       <c r="O23">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="P23">
-        <v>6.25</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q23">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="R23">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="S23">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="T23">
-        <v>3.58</v>
+        <v>3.26</v>
       </c>
       <c r="U23">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W23">
         <v>1.04</v>
       </c>
       <c r="X23">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="Z23">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AA23">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="AB23">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC23">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AD23">
-        <v>5.44</v>
+        <v>4.2</v>
       </c>
       <c r="AE23">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF23">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AG23">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AH23">
-        <v>11</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AI23">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AJ23" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AK23" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AL23">
         <v>1.36</v>
       </c>
       <c r="AM23">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AN23">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AO23">
         <v>-1</v>
       </c>
       <c r="AP23">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ23">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AR23">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AS23">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AT23">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AU23">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AV23">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AW23">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX23">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AY23">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ23">
         <v>0</v>
@@ -4707,13 +4740,13 @@
         <v>0</v>
       </c>
       <c r="BB23">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="BC23">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="BD23" s="3">
-        <v>45828.79166666666</v>
+        <v>45828.66666666666</v>
       </c>
     </row>
     <row r="24" spans="1:56">
@@ -4721,19 +4754,19 @@
         <v>45828</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E24" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F24" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -4748,94 +4781,94 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L24">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="M24">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N24">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="O24">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="P24">
-        <v>11</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q24">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="R24">
+        <v>1.41</v>
+      </c>
+      <c r="S24">
+        <v>2.65</v>
+      </c>
+      <c r="T24">
+        <v>2.93</v>
+      </c>
+      <c r="U24">
         <v>1.35</v>
       </c>
-      <c r="S24">
-        <v>2.85</v>
-      </c>
-      <c r="T24">
-        <v>2.62</v>
-      </c>
-      <c r="U24">
-        <v>1.45</v>
-      </c>
       <c r="V24">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
       <c r="W24">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y24">
-        <v>10.4</v>
+        <v>9</v>
       </c>
       <c r="Z24">
+        <v>1.33</v>
+      </c>
+      <c r="AA24">
+        <v>3.2</v>
+      </c>
+      <c r="AB24">
+        <v>2</v>
+      </c>
+      <c r="AC24">
+        <v>1.75</v>
+      </c>
+      <c r="AD24">
+        <v>3.6</v>
+      </c>
+      <c r="AE24">
         <v>1.25</v>
       </c>
-      <c r="AA24">
-        <v>3.74</v>
-      </c>
-      <c r="AB24">
-        <v>1.78</v>
-      </c>
-      <c r="AC24">
-        <v>1.94</v>
-      </c>
-      <c r="AD24">
-        <v>2.8</v>
-      </c>
-      <c r="AE24">
-        <v>1.37</v>
-      </c>
       <c r="AF24">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AG24">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AH24">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AI24">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AJ24" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AK24" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AL24">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AM24">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AN24">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="AO24">
         <v>-1</v>
@@ -4877,13 +4910,13 @@
         <v>0</v>
       </c>
       <c r="BB24">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="BC24">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="BD24" s="3">
-        <v>45828.83333333334</v>
+        <v>45828.66666666666</v>
       </c>
     </row>
     <row r="25" spans="1:56">
@@ -4891,19 +4924,19 @@
         <v>45828</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E25" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F25" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -4918,127 +4951,127 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L25">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="M25">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N25">
-        <v>2.07</v>
+        <v>2.65</v>
       </c>
       <c r="O25">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="P25">
-        <v>13.5</v>
+        <v>8</v>
       </c>
       <c r="Q25">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="R25">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="S25">
-        <v>2.85</v>
+        <v>2.48</v>
       </c>
       <c r="T25">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="U25">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="V25">
-        <v>6.15</v>
+        <v>8</v>
       </c>
       <c r="W25">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z25">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AA25">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="AB25">
-        <v>1.75</v>
+        <v>2.28</v>
       </c>
       <c r="AC25">
-        <v>1.97</v>
+        <v>1.58</v>
       </c>
       <c r="AD25">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="AE25">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="AF25">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AG25">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AH25">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="AI25">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AJ25" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AK25" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AL25">
-        <v>1.22</v>
+        <v>1.46</v>
       </c>
       <c r="AM25">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AN25">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AO25">
         <v>-1</v>
       </c>
       <c r="AP25">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AU25">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AV25">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AW25">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX25">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY25">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ25">
         <v>0</v>
@@ -5047,13 +5080,13 @@
         <v>0</v>
       </c>
       <c r="BB25">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="BC25">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="BD25" s="3">
-        <v>45828.85416666666</v>
+        <v>45828.77083333334</v>
       </c>
     </row>
     <row r="26" spans="1:56">
@@ -5061,19 +5094,19 @@
         <v>45828</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s">
         <v>78</v>
       </c>
       <c r="D26" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E26" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F26" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5088,94 +5121,94 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L26">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M26">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N26">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O26">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P26">
         <v>0</v>
       </c>
       <c r="Q26">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V26">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z26">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA26">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB26">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AC26">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD26">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE26">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AF26">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG26">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH26">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AI26">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AK26" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AL26">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AM26">
         <v>0</v>
       </c>
       <c r="AN26">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO26">
         <v>-1</v>
@@ -5217,13 +5250,13 @@
         <v>0</v>
       </c>
       <c r="BB26">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BC26">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BD26" s="3">
-        <v>45828.85416666666</v>
+        <v>45828.79166666666</v>
       </c>
     </row>
     <row r="27" spans="1:56">
@@ -5231,19 +5264,19 @@
         <v>45828</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C27" t="s">
         <v>79</v>
       </c>
       <c r="D27" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E27" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F27" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -5258,127 +5291,127 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L27">
-        <v>1.49</v>
+        <v>2.55</v>
       </c>
       <c r="M27">
-        <v>3.95</v>
+        <v>2.92</v>
       </c>
       <c r="N27">
-        <v>5.2</v>
+        <v>3.15</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R27">
+        <v>1.7</v>
+      </c>
+      <c r="S27">
+        <v>1.97</v>
+      </c>
+      <c r="T27">
+        <v>3.7</v>
+      </c>
+      <c r="U27">
+        <v>1.2</v>
+      </c>
+      <c r="V27">
+        <v>12.5</v>
+      </c>
+      <c r="W27">
+        <v>1.04</v>
+      </c>
+      <c r="X27">
+        <v>1.11</v>
+      </c>
+      <c r="Y27">
+        <v>5.5</v>
+      </c>
+      <c r="Z27">
+        <v>1.65</v>
+      </c>
+      <c r="AA27">
+        <v>2.2</v>
+      </c>
+      <c r="AB27">
+        <v>2.88</v>
+      </c>
+      <c r="AC27">
+        <v>1.36</v>
+      </c>
+      <c r="AD27">
+        <v>5.3</v>
+      </c>
+      <c r="AE27">
+        <v>1.11</v>
+      </c>
+      <c r="AF27">
+        <v>2.15</v>
+      </c>
+      <c r="AG27">
+        <v>1.57</v>
+      </c>
+      <c r="AH27">
+        <v>15</v>
+      </c>
+      <c r="AI27">
+        <v>1.01</v>
+      </c>
+      <c r="AJ27" t="s">
+        <v>152</v>
+      </c>
+      <c r="AK27" t="s">
+        <v>152</v>
+      </c>
+      <c r="AL27">
         <v>1.4</v>
       </c>
-      <c r="S27">
-        <v>2.7</v>
-      </c>
-      <c r="T27">
-        <v>2.9</v>
-      </c>
-      <c r="U27">
+      <c r="AM27">
         <v>1.36</v>
       </c>
-      <c r="V27">
-        <v>7.3</v>
-      </c>
-      <c r="W27">
-        <v>1.07</v>
-      </c>
-      <c r="X27">
-        <v>1.03</v>
-      </c>
-      <c r="Y27">
-        <v>7.65</v>
-      </c>
-      <c r="Z27">
-        <v>1.33</v>
-      </c>
-      <c r="AA27">
-        <v>3.04</v>
-      </c>
-      <c r="AB27">
-        <v>1.75</v>
-      </c>
-      <c r="AC27">
-        <v>1.95</v>
-      </c>
-      <c r="AD27">
-        <v>3.4</v>
-      </c>
-      <c r="AE27">
-        <v>1.22</v>
-      </c>
-      <c r="AF27">
-        <v>1.95</v>
-      </c>
-      <c r="AG27">
-        <v>1.75</v>
-      </c>
-      <c r="AH27">
-        <v>6.1</v>
-      </c>
-      <c r="AI27">
-        <v>1.08</v>
-      </c>
-      <c r="AJ27" t="s">
-        <v>141</v>
-      </c>
-      <c r="AK27" t="s">
-        <v>141</v>
-      </c>
-      <c r="AL27">
-        <v>1.18</v>
-      </c>
-      <c r="AM27">
-        <v>0</v>
-      </c>
       <c r="AN27">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AO27">
         <v>-1</v>
       </c>
       <c r="AP27">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AU27">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AV27">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW27">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AX27">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY27">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AZ27">
         <v>0</v>
@@ -5387,13 +5420,13 @@
         <v>0</v>
       </c>
       <c r="BB27">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BC27">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD27" s="3">
-        <v>45828.875</v>
+        <v>45828.79166666666</v>
       </c>
     </row>
     <row r="28" spans="1:56">
@@ -5401,19 +5434,19 @@
         <v>45828</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D28" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E28" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F28" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -5428,94 +5461,94 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L28">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="M28">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N28">
+        <v>2.7</v>
+      </c>
+      <c r="O28">
+        <v>1.83</v>
+      </c>
+      <c r="P28">
+        <v>11</v>
+      </c>
+      <c r="Q28">
+        <v>2.1</v>
+      </c>
+      <c r="R28">
+        <v>1.4</v>
+      </c>
+      <c r="S28">
+        <v>2.65</v>
+      </c>
+      <c r="T28">
+        <v>2.75</v>
+      </c>
+      <c r="U28">
+        <v>1.38</v>
+      </c>
+      <c r="V28">
+        <v>6.2</v>
+      </c>
+      <c r="W28">
+        <v>1.08</v>
+      </c>
+      <c r="X28">
+        <v>1</v>
+      </c>
+      <c r="Y28">
+        <v>9.65</v>
+      </c>
+      <c r="Z28">
+        <v>1.29</v>
+      </c>
+      <c r="AA28">
+        <v>3.3</v>
+      </c>
+      <c r="AB28">
+        <v>1.83</v>
+      </c>
+      <c r="AC28">
+        <v>1.8</v>
+      </c>
+      <c r="AD28">
+        <v>3</v>
+      </c>
+      <c r="AE28">
+        <v>1.3</v>
+      </c>
+      <c r="AF28">
         <v>1.73</v>
       </c>
-      <c r="O28">
-        <v>0</v>
-      </c>
-      <c r="P28">
-        <v>0</v>
-      </c>
-      <c r="Q28">
-        <v>0</v>
-      </c>
-      <c r="R28">
-        <v>1.5</v>
-      </c>
-      <c r="S28">
-        <v>2.4</v>
-      </c>
-      <c r="T28">
-        <v>3.28</v>
-      </c>
-      <c r="U28">
-        <v>1.29</v>
-      </c>
-      <c r="V28">
-        <v>8.5</v>
-      </c>
-      <c r="W28">
-        <v>1.04</v>
-      </c>
-      <c r="X28">
-        <v>1.07</v>
-      </c>
-      <c r="Y28">
-        <v>7</v>
-      </c>
-      <c r="Z28">
-        <v>1.42</v>
-      </c>
-      <c r="AA28">
-        <v>2.62</v>
-      </c>
-      <c r="AB28">
-        <v>2.03</v>
-      </c>
-      <c r="AC28">
-        <v>1.69</v>
-      </c>
-      <c r="AD28">
-        <v>4</v>
-      </c>
-      <c r="AE28">
-        <v>1.2</v>
-      </c>
-      <c r="AF28">
-        <v>1.95</v>
-      </c>
       <c r="AG28">
-        <v>1.73</v>
+        <v>2.14</v>
       </c>
       <c r="AH28">
-        <v>8.5</v>
+        <v>6.55</v>
       </c>
       <c r="AI28">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ28" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AK28" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AL28">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AM28">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN28">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AO28">
         <v>-1</v>
@@ -5524,10 +5557,10 @@
         <v>0</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS28">
         <v>0</v>
@@ -5539,10 +5572,10 @@
         <v>0</v>
       </c>
       <c r="AV28">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AW28">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX28">
         <v>0</v>
@@ -5557,13 +5590,13 @@
         <v>0</v>
       </c>
       <c r="BB28">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BC28">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD28" s="3">
-        <v>45828.875</v>
+        <v>45828.83333333334</v>
       </c>
     </row>
     <row r="29" spans="1:56">
@@ -5577,13 +5610,13 @@
         <v>80</v>
       </c>
       <c r="D29" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E29" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F29" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -5598,94 +5631,94 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AI29">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ29" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AK29" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO29">
         <v>-1</v>
@@ -5727,13 +5760,13 @@
         <v>0</v>
       </c>
       <c r="BB29">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BC29">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BD29" s="3">
-        <v>45828.875</v>
+        <v>45828.85416666666</v>
       </c>
     </row>
     <row r="30" spans="1:56">
@@ -5741,19 +5774,19 @@
         <v>45828</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D30" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E30" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F30" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -5768,141 +5801,821 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L30">
-        <v>1.81</v>
+        <v>2.94</v>
       </c>
       <c r="M30">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N30">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="O30">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="P30">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q30">
-        <v>3.1</v>
+        <v>1.67</v>
       </c>
       <c r="R30">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="S30">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="T30">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="U30">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="V30">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="W30">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X30">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Z30">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AA30">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="AB30">
+        <v>1.7</v>
+      </c>
+      <c r="AC30">
+        <v>2</v>
+      </c>
+      <c r="AD30">
+        <v>2.8</v>
+      </c>
+      <c r="AE30">
+        <v>1.37</v>
+      </c>
+      <c r="AF30">
+        <v>1.55</v>
+      </c>
+      <c r="AG30">
         <v>2.2</v>
       </c>
-      <c r="AC30">
-        <v>1.55</v>
-      </c>
-      <c r="AD30">
-        <v>4.33</v>
-      </c>
-      <c r="AE30">
-        <v>1.17</v>
-      </c>
-      <c r="AF30">
-        <v>2.05</v>
-      </c>
-      <c r="AG30">
-        <v>1.7</v>
-      </c>
       <c r="AH30">
-        <v>8.5</v>
+        <v>5.7</v>
       </c>
       <c r="AI30">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AJ30" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AK30" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AL30">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AM30">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AN30">
-        <v>1.91</v>
+        <v>1.27</v>
       </c>
       <c r="AO30">
         <v>-1</v>
       </c>
       <c r="AP30">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ30">
+        <v>0</v>
+      </c>
+      <c r="AR30">
+        <v>0</v>
+      </c>
+      <c r="AS30">
+        <v>0</v>
+      </c>
+      <c r="AT30">
+        <v>0</v>
+      </c>
+      <c r="AU30">
+        <v>0</v>
+      </c>
+      <c r="AV30">
+        <v>0</v>
+      </c>
+      <c r="AW30">
+        <v>0</v>
+      </c>
+      <c r="AX30">
+        <v>0</v>
+      </c>
+      <c r="AY30">
+        <v>0</v>
+      </c>
+      <c r="AZ30">
+        <v>0</v>
+      </c>
+      <c r="BA30">
+        <v>0</v>
+      </c>
+      <c r="BB30">
+        <v>2.3</v>
+      </c>
+      <c r="BC30">
+        <v>1.67</v>
+      </c>
+      <c r="BD30" s="3">
+        <v>45828.85416666666</v>
+      </c>
+    </row>
+    <row r="31" spans="1:56">
+      <c r="A31" s="2">
+        <v>45828</v>
+      </c>
+      <c r="B31" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" t="s">
+        <v>81</v>
+      </c>
+      <c r="D31" t="s">
+        <v>83</v>
+      </c>
+      <c r="E31" t="s">
+        <v>114</v>
+      </c>
+      <c r="F31" t="s">
+        <v>147</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31" t="s">
+        <v>151</v>
+      </c>
+      <c r="L31">
+        <v>1.45</v>
+      </c>
+      <c r="M31">
+        <v>4.1</v>
+      </c>
+      <c r="N31">
+        <v>5.5</v>
+      </c>
+      <c r="O31">
+        <v>1.33</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>3.25</v>
+      </c>
+      <c r="R31">
+        <v>1.22</v>
+      </c>
+      <c r="S31">
+        <v>3.6</v>
+      </c>
+      <c r="T31">
+        <v>2.05</v>
+      </c>
+      <c r="U31">
+        <v>1.62</v>
+      </c>
+      <c r="V31">
+        <v>4.75</v>
+      </c>
+      <c r="W31">
+        <v>1.15</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>1.12</v>
+      </c>
+      <c r="AA31">
+        <v>5.1</v>
+      </c>
+      <c r="AB31">
+        <v>1.43</v>
+      </c>
+      <c r="AC31">
+        <v>2.6</v>
+      </c>
+      <c r="AD31">
+        <v>2.1</v>
+      </c>
+      <c r="AE31">
+        <v>1.65</v>
+      </c>
+      <c r="AF31">
+        <v>1.57</v>
+      </c>
+      <c r="AG31">
+        <v>2.15</v>
+      </c>
+      <c r="AH31">
+        <v>3.4</v>
+      </c>
+      <c r="AI31">
+        <v>1.26</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>152</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>152</v>
+      </c>
+      <c r="AL31">
+        <v>1.1</v>
+      </c>
+      <c r="AM31">
+        <v>0</v>
+      </c>
+      <c r="AN31">
+        <v>2.45</v>
+      </c>
+      <c r="AO31">
+        <v>-1</v>
+      </c>
+      <c r="AP31">
+        <v>0</v>
+      </c>
+      <c r="AQ31">
+        <v>0</v>
+      </c>
+      <c r="AR31">
+        <v>0</v>
+      </c>
+      <c r="AS31">
+        <v>0</v>
+      </c>
+      <c r="AT31">
+        <v>0</v>
+      </c>
+      <c r="AU31">
+        <v>0</v>
+      </c>
+      <c r="AV31">
+        <v>0</v>
+      </c>
+      <c r="AW31">
+        <v>0</v>
+      </c>
+      <c r="AX31">
+        <v>0</v>
+      </c>
+      <c r="AY31">
+        <v>0</v>
+      </c>
+      <c r="AZ31">
+        <v>0</v>
+      </c>
+      <c r="BA31">
+        <v>0</v>
+      </c>
+      <c r="BB31">
+        <v>1.33</v>
+      </c>
+      <c r="BC31">
+        <v>3.25</v>
+      </c>
+      <c r="BD31" s="3">
+        <v>45828.875</v>
+      </c>
+    </row>
+    <row r="32" spans="1:56">
+      <c r="A32" s="2">
+        <v>45828</v>
+      </c>
+      <c r="B32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32" t="s">
+        <v>83</v>
+      </c>
+      <c r="E32" t="s">
+        <v>115</v>
+      </c>
+      <c r="F32" t="s">
+        <v>148</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32" t="s">
+        <v>151</v>
+      </c>
+      <c r="L32">
+        <v>1.4</v>
+      </c>
+      <c r="M32">
+        <v>3.75</v>
+      </c>
+      <c r="N32">
+        <v>6.8</v>
+      </c>
+      <c r="O32">
+        <v>1.25</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>4.5</v>
+      </c>
+      <c r="R32">
+        <v>1.36</v>
+      </c>
+      <c r="S32">
+        <v>2.8</v>
+      </c>
+      <c r="T32">
+        <v>2.4</v>
+      </c>
+      <c r="U32">
+        <v>1.4</v>
+      </c>
+      <c r="V32">
+        <v>6.3</v>
+      </c>
+      <c r="W32">
+        <v>1.08</v>
+      </c>
+      <c r="X32">
+        <v>1.02</v>
+      </c>
+      <c r="Y32">
+        <v>9</v>
+      </c>
+      <c r="Z32">
+        <v>1.29</v>
+      </c>
+      <c r="AA32">
+        <v>3.3</v>
+      </c>
+      <c r="AB32">
+        <v>1.83</v>
+      </c>
+      <c r="AC32">
+        <v>1.81</v>
+      </c>
+      <c r="AD32">
+        <v>2.95</v>
+      </c>
+      <c r="AE32">
         <v>1.3</v>
       </c>
-      <c r="AR30">
-        <v>1.67</v>
-      </c>
-      <c r="AS30">
+      <c r="AF32">
+        <v>2.1</v>
+      </c>
+      <c r="AG32">
+        <v>1.62</v>
+      </c>
+      <c r="AH32">
+        <v>6</v>
+      </c>
+      <c r="AI32">
+        <v>1.09</v>
+      </c>
+      <c r="AJ32" t="s">
+        <v>152</v>
+      </c>
+      <c r="AK32" t="s">
+        <v>152</v>
+      </c>
+      <c r="AL32">
+        <v>1.14</v>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+      <c r="AN32">
+        <v>2.7</v>
+      </c>
+      <c r="AO32">
+        <v>-1</v>
+      </c>
+      <c r="AP32">
+        <v>1.28</v>
+      </c>
+      <c r="AQ32">
+        <v>1.52</v>
+      </c>
+      <c r="AR32">
+        <v>2.12</v>
+      </c>
+      <c r="AS32">
+        <v>2.37</v>
+      </c>
+      <c r="AT32">
+        <v>3.07</v>
+      </c>
+      <c r="AU32">
+        <v>3.2</v>
+      </c>
+      <c r="AV32">
+        <v>2.36</v>
+      </c>
+      <c r="AW32">
         <v>1.87</v>
       </c>
-      <c r="AT30">
-        <v>2.34</v>
-      </c>
-      <c r="AU30">
-        <v>4.35</v>
-      </c>
-      <c r="AV30">
-        <v>3.07</v>
-      </c>
-      <c r="AW30">
+      <c r="AX32">
+        <v>1.55</v>
+      </c>
+      <c r="AY32">
+        <v>1.32</v>
+      </c>
+      <c r="AZ32">
+        <v>0</v>
+      </c>
+      <c r="BA32">
+        <v>0</v>
+      </c>
+      <c r="BB32">
+        <v>1.25</v>
+      </c>
+      <c r="BC32">
+        <v>4.5</v>
+      </c>
+      <c r="BD32" s="3">
+        <v>45828.875</v>
+      </c>
+    </row>
+    <row r="33" spans="1:56">
+      <c r="A33" s="2">
+        <v>45828</v>
+      </c>
+      <c r="B33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" t="s">
+        <v>82</v>
+      </c>
+      <c r="D33" t="s">
+        <v>83</v>
+      </c>
+      <c r="E33" t="s">
+        <v>116</v>
+      </c>
+      <c r="F33" t="s">
+        <v>149</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33" t="s">
+        <v>151</v>
+      </c>
+      <c r="L33">
+        <v>4.33</v>
+      </c>
+      <c r="M33">
+        <v>3.75</v>
+      </c>
+      <c r="N33">
+        <v>1.76</v>
+      </c>
+      <c r="O33">
+        <v>2.88</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>1.53</v>
+      </c>
+      <c r="R33">
+        <v>1.36</v>
+      </c>
+      <c r="S33">
+        <v>2.7</v>
+      </c>
+      <c r="T33">
+        <v>3.22</v>
+      </c>
+      <c r="U33">
+        <v>1.28</v>
+      </c>
+      <c r="V33">
+        <v>7</v>
+      </c>
+      <c r="W33">
+        <v>1.04</v>
+      </c>
+      <c r="X33">
+        <v>1.05</v>
+      </c>
+      <c r="Y33">
+        <v>8.5</v>
+      </c>
+      <c r="Z33">
+        <v>1.35</v>
+      </c>
+      <c r="AA33">
+        <v>2.74</v>
+      </c>
+      <c r="AB33">
+        <v>2.08</v>
+      </c>
+      <c r="AC33">
+        <v>1.59</v>
+      </c>
+      <c r="AD33">
+        <v>4.33</v>
+      </c>
+      <c r="AE33">
+        <v>1.22</v>
+      </c>
+      <c r="AF33">
+        <v>1.91</v>
+      </c>
+      <c r="AG33">
+        <v>1.8</v>
+      </c>
+      <c r="AH33">
+        <v>6.5</v>
+      </c>
+      <c r="AI33">
+        <v>1.1</v>
+      </c>
+      <c r="AJ33" t="s">
+        <v>152</v>
+      </c>
+      <c r="AK33" t="s">
+        <v>152</v>
+      </c>
+      <c r="AL33">
+        <v>1.2</v>
+      </c>
+      <c r="AM33">
+        <v>0</v>
+      </c>
+      <c r="AN33">
+        <v>1.18</v>
+      </c>
+      <c r="AO33">
+        <v>-1</v>
+      </c>
+      <c r="AP33">
+        <v>1.36</v>
+      </c>
+      <c r="AQ33">
+        <v>1.63</v>
+      </c>
+      <c r="AR33">
+        <v>2.33</v>
+      </c>
+      <c r="AS33">
+        <v>2.55</v>
+      </c>
+      <c r="AT33">
+        <v>3.38</v>
+      </c>
+      <c r="AU33">
+        <v>2.87</v>
+      </c>
+      <c r="AV33">
+        <v>2.2</v>
+      </c>
+      <c r="AW33">
+        <v>1.74</v>
+      </c>
+      <c r="AX33">
+        <v>1.45</v>
+      </c>
+      <c r="AY33">
+        <v>1.26</v>
+      </c>
+      <c r="AZ33">
+        <v>0</v>
+      </c>
+      <c r="BA33">
+        <v>0</v>
+      </c>
+      <c r="BB33">
+        <v>2.88</v>
+      </c>
+      <c r="BC33">
+        <v>1.53</v>
+      </c>
+      <c r="BD33" s="3">
+        <v>45828.875</v>
+      </c>
+    </row>
+    <row r="34" spans="1:56">
+      <c r="A34" s="2">
+        <v>45828</v>
+      </c>
+      <c r="B34" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" t="s">
+        <v>79</v>
+      </c>
+      <c r="D34" t="s">
+        <v>83</v>
+      </c>
+      <c r="E34" t="s">
+        <v>117</v>
+      </c>
+      <c r="F34" t="s">
+        <v>150</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34" t="s">
+        <v>151</v>
+      </c>
+      <c r="L34">
+        <v>1.8</v>
+      </c>
+      <c r="M34">
+        <v>3.15</v>
+      </c>
+      <c r="N34">
+        <v>4</v>
+      </c>
+      <c r="O34">
+        <v>1.5</v>
+      </c>
+      <c r="P34">
+        <v>7</v>
+      </c>
+      <c r="Q34">
+        <v>3.1</v>
+      </c>
+      <c r="R34">
+        <v>1.45</v>
+      </c>
+      <c r="S34">
+        <v>2.45</v>
+      </c>
+      <c r="T34">
+        <v>3.36</v>
+      </c>
+      <c r="U34">
+        <v>1.31</v>
+      </c>
+      <c r="V34">
+        <v>6.8</v>
+      </c>
+      <c r="W34">
+        <v>1.06</v>
+      </c>
+      <c r="X34">
+        <v>1.08</v>
+      </c>
+      <c r="Y34">
+        <v>7.5</v>
+      </c>
+      <c r="Z34">
+        <v>1.39</v>
+      </c>
+      <c r="AA34">
+        <v>2.75</v>
+      </c>
+      <c r="AB34">
+        <v>2.3</v>
+      </c>
+      <c r="AC34">
+        <v>1.55</v>
+      </c>
+      <c r="AD34">
+        <v>4.4</v>
+      </c>
+      <c r="AE34">
+        <v>1.2</v>
+      </c>
+      <c r="AF34">
         <v>2.05</v>
       </c>
-      <c r="AX30">
-        <v>1.87</v>
-      </c>
-      <c r="AY30">
-        <v>1.56</v>
-      </c>
-      <c r="AZ30">
-        <v>0</v>
-      </c>
-      <c r="BA30">
-        <v>0</v>
-      </c>
-      <c r="BB30">
+      <c r="AG34">
+        <v>1.7</v>
+      </c>
+      <c r="AH34">
+        <v>9.5</v>
+      </c>
+      <c r="AI34">
+        <v>1.06</v>
+      </c>
+      <c r="AJ34" t="s">
+        <v>152</v>
+      </c>
+      <c r="AK34" t="s">
+        <v>152</v>
+      </c>
+      <c r="AL34">
+        <v>1.33</v>
+      </c>
+      <c r="AM34">
+        <v>1.31</v>
+      </c>
+      <c r="AN34">
+        <v>1.85</v>
+      </c>
+      <c r="AO34">
+        <v>-1</v>
+      </c>
+      <c r="AP34">
+        <v>1.16</v>
+      </c>
+      <c r="AQ34">
+        <v>1.42</v>
+      </c>
+      <c r="AR34">
+        <v>1.69</v>
+      </c>
+      <c r="AS34">
+        <v>1.89</v>
+      </c>
+      <c r="AT34">
+        <v>2.33</v>
+      </c>
+      <c r="AU34">
+        <v>4.25</v>
+      </c>
+      <c r="AV34">
+        <v>3.05</v>
+      </c>
+      <c r="AW34">
+        <v>2.33</v>
+      </c>
+      <c r="AX34">
+        <v>1.85</v>
+      </c>
+      <c r="AY34">
+        <v>1.53</v>
+      </c>
+      <c r="AZ34">
+        <v>0</v>
+      </c>
+      <c r="BA34">
+        <v>0</v>
+      </c>
+      <c r="BB34">
         <v>1.5</v>
       </c>
-      <c r="BC30">
+      <c r="BC34">
         <v>3.1</v>
       </c>
-      <c r="BD30" s="3">
+      <c r="BD34" s="3">
         <v>45828.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-06-20.xlsx
+++ b/jogos_2025-06-20.xlsx
@@ -784,27 +784,27 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['23', '29', '76', '79']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG3" t="n">
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.4</v>
+        <v>6.59</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9</v>
+        <v>3.63</v>
       </c>
       <c r="N4" t="n">
-        <v>10.2</v>
+        <v>1.55</v>
       </c>
       <c r="O4" t="n">
-        <v>1.99</v>
+        <v>6.7</v>
       </c>
       <c r="P4" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.8</v>
+        <v>1.8</v>
       </c>
       <c r="R4" t="n">
         <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="T4" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="U4" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '75', '68']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.55</v>
+        <v>1.08</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.88</v>
+        <v>1.44</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45828.5</v>
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>6.59</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
-        <v>3.63</v>
+        <v>3.9</v>
       </c>
       <c r="N5" t="n">
-        <v>1.55</v>
+        <v>10.2</v>
       </c>
       <c r="O5" t="n">
-        <v>6.7</v>
+        <v>1.99</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.8</v>
+        <v>6.8</v>
       </c>
       <c r="R5" t="n">
         <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="T5" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>2.88</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>['59']</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>['7', '75', '68']</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.44</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45828.5</v>
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>3.51</v>
       </c>
       <c r="N8" t="n">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="O8" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,109 +1804,109 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y11" t="n">
         <v>2</v>
       </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P11" t="n">
+      <c r="Z11" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>['5', '10', '39']</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI11" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q11" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>['45', '45+3']</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>['71']</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>3</v>
-      </c>
       <c r="AJ11" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45828.65625</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.95</v>
+        <v>2.92</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="N12" t="n">
-        <v>3.35</v>
+        <v>2.42</v>
       </c>
       <c r="O12" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1</v>
+        <v>2.51</v>
       </c>
       <c r="T12" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W12" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="X12" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2', '11', '35']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.77</v>
+        <v>1.41</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.69</v>
+        <v>2.1</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45828.65625</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,19 +2062,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
         <v>1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.73</v>
+        <v>3.2</v>
       </c>
       <c r="M13" t="n">
-        <v>3.76</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>4.6</v>
+        <v>2.05</v>
       </c>
       <c r="O13" t="n">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="P13" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.9</v>
+        <v>2.65</v>
       </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="T13" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U13" t="n">
         <v>1.4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W13" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="X13" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['3']</t>
+          <t>['88', '1']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.15</v>
+        <v>1.32</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.88</v>
+        <v>1.62</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45828.65625</v>
@@ -2191,16 +2191,16 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="M14" t="n">
-        <v>4.14</v>
+        <v>3.88</v>
       </c>
       <c r="N14" t="n">
-        <v>4.59</v>
+        <v>6.7</v>
       </c>
       <c r="O14" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="P14" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="T14" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="U14" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W14" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X14" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['6']</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.2</v>
+        <v>2.93</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45828.65625</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,19 +2449,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.64</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA16" t="n">
         <v>2.9</v>
       </c>
-      <c r="O16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.68</v>
+        <v>2.07</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2538,20 +2538,20 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.45</v>
+        <v>1.77</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45828.65625</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,22 +2578,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.76</v>
+        <v>3.34</v>
       </c>
       <c r="M17" t="n">
-        <v>3.88</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>6.7</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
-        <v>2.35</v>
+        <v>3.75</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.6</v>
+        <v>2.72</v>
       </c>
       <c r="R17" t="n">
         <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="U17" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="V17" t="n">
         <v>1.04</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="X17" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['45', '45+3']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
         <v>1.7</v>
       </c>
-      <c r="Z17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['89']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['90+2']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH17" t="n">
-        <v>2.93</v>
+        <v>1.25</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.34</v>
+        <v>3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.4</v>
+        <v>1.44</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45828.65625</v>
@@ -2707,25 +2707,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.92</v>
+        <v>2.64</v>
       </c>
       <c r="M18" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="N18" t="n">
-        <v>2.42</v>
+        <v>2.9</v>
       </c>
       <c r="O18" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P18" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.7</v>
+        <v>3.65</v>
       </c>
       <c r="R18" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="S18" t="n">
-        <v>2.51</v>
+        <v>2.25</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="V18" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="W18" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="Y18" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC18" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.99</v>
+        <v>1.68</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['2', '11', '35']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['33']</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45828.65625</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.05</v>
+        <v>1.73</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.76</v>
       </c>
       <c r="N19" t="n">
-        <v>2.16</v>
+        <v>4.6</v>
       </c>
       <c r="O19" t="n">
-        <v>3.43</v>
+        <v>2.38</v>
       </c>
       <c r="P19" t="n">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.65</v>
+        <v>4.9</v>
       </c>
       <c r="R19" t="n">
         <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T19" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U19" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X19" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
+          <t>['3']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['5', '10', '39']</t>
-        </is>
-      </c>
       <c r="AG19" t="n">
-        <v>1.62</v>
+        <v>1.27</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.33</v>
+        <v>2.15</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.95</v>
+        <v>2.88</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45828.65625</v>
@@ -2965,109 +2965,109 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
       </c>
       <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
         <v>1</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.2</v>
+        <v>1.64</v>
       </c>
       <c r="M20" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S20" t="n">
         <v>3.6</v>
       </c>
-      <c r="N20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.85</v>
-      </c>
       <c r="T20" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="V20" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.86</v>
+        <v>1.54</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="AA20" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AD20" t="n">
         <v>2.1</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['88', '1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.32</v>
+        <v>2.2</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.62</v>
+        <v>2.8</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45828.65625</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,109 +3094,109 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
       </c>
       <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
-        <v>2.4</v>
-      </c>
       <c r="M21" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O21" t="n">
-        <v>3.52</v>
+        <v>2.74</v>
       </c>
       <c r="P21" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="R21" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="S21" t="n">
-        <v>1.98</v>
+        <v>2.55</v>
       </c>
       <c r="T21" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="V21" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="W21" t="n">
-        <v>1.69</v>
+        <v>1.41</v>
       </c>
       <c r="X21" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AA21" t="n">
-        <v>6.47</v>
+        <v>4.75</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['88', '10']</t>
+          <t>['5', '61']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['16', '59', '45+2']</t>
+          <t>['23', '54']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45828.66666666666</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="M22" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
-        <v>2.74</v>
+        <v>3.52</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="R22" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.5</v>
       </c>
-      <c r="S22" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['5', '61']</t>
+          <t>['88', '10']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['23', '54']</t>
+          <t>['16', '59', '45+2']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.29</v>
+        <v>2.63</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45828.66666666666</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,29 +3610,29 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3694,12 +3694,12 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['10', '29', '44', '67']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['62']</t>
         </is>
       </c>
       <c r="AG25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,29 +3739,29 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['10', '29', '44', '67']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['62']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG26" t="n">
@@ -4126,22 +4126,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -4152,77 +4152,77 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="M29" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="O29" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P29" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="Q29" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S29" t="n">
         <v>2.8</v>
       </c>
-      <c r="R29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.25</v>
-      </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="U29" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X29" t="n">
         <v>3.9</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="AB29" t="n">
         <v>1.42</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['16', '43', '56']</t>
+          <t>['45', '66']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['48']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AI29" t="n">
         <v>2.3</v>
@@ -4255,23 +4255,23 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
         <v>2</v>
       </c>
-      <c r="H30" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1</v>
-      </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
@@ -4281,77 +4281,77 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="M30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O30" t="n">
         <v>3.4</v>
       </c>
-      <c r="N30" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O30" t="n">
-        <v>3.45</v>
-      </c>
       <c r="P30" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="T30" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X30" t="n">
         <v>3.9</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="AB30" t="n">
         <v>1.42</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['45', '66']</t>
+          <t>['16', '43', '56']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['48']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AI30" t="n">
         <v>2.3</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,22 +4384,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G31" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" t="n">
         <v>1</v>
       </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="M31" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="O31" t="n">
-        <v>1.91</v>
+        <v>2.88</v>
       </c>
       <c r="P31" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.84</v>
+        <v>3.75</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="T31" t="n">
-        <v>2.48</v>
+        <v>3.25</v>
       </c>
       <c r="U31" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="V31" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="W31" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="X31" t="n">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.5</v>
+        <v>3.79</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>['13', '21', '38', '83']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1</v>
+        <v>1.31</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.8</v>
+        <v>1.66</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AJ31" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45828.875</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,109 +4513,109 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G32" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M32" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="N32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S32" t="n">
         <v>4</v>
       </c>
-      <c r="H32" t="n">
+      <c r="T32" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V32" t="n">
         <v>1</v>
       </c>
-      <c r="I32" t="n">
-        <v>3</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="M32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T32" t="n">
+      <c r="W32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X32" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>['19', '71', '22']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>['13', '61', '86']</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AJ32" t="n">
         <v>3.25</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X32" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>['13', '21', '38', '83']</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>['50']</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45828.875</v>
@@ -4642,109 +4642,109 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N33" t="n">
+        <v>7</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>4</v>
-      </c>
-      <c r="M33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="O33" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S33" t="n">
+      <c r="AH33" t="n">
         <v>2.8</v>
       </c>
-      <c r="T33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB33" t="n">
+      <c r="AI33" t="n">
         <v>1.25</v>
       </c>
-      <c r="AC33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>['30', '68']</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AJ33" t="n">
-        <v>1.53</v>
+        <v>4.5</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45828.875</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,25 +4771,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>4</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O34" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="R34" t="n">
         <v>1.34</v>
       </c>
-      <c r="M34" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="N34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O34" t="n">
+      <c r="S34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z34" t="n">
         <v>1.75</v>
       </c>
-      <c r="P34" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S34" t="n">
-        <v>4</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X34" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AA34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC34" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB34" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC34" t="n">
+      <c r="AD34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>['30', '68']</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AJ34" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>['19', '71', '22']</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>['13', '61', '86']</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>3.25</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45828.875</v>
